--- a/packages/calculators/src/modules/test/3.4-sheep-enteric/3.4-sheep-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.4-sheep-enteric/3.4-sheep-enteric.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/3.4-sheep-enteric/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/3.4-sheep-enteric/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3994BA4F-1F0C-5948-B0BB-8BACC51AC299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69718916-B6D8-D045-874B-15640B66E8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="11260" windowWidth="28800" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13520" yWindow="-20580" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.4.1.1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="127">
   <si>
     <t>(LRjk=3,4 * min( LMRjk=3,4  100)) / 100</t>
   </si>
@@ -11323,7 +11323,7 @@
         <v>72.67278741355095</v>
       </c>
     </row>
-    <row r="177" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>5</v>
       </c>
@@ -11389,7 +11389,7 @@
         <v>57.740873907285312</v>
       </c>
     </row>
-    <row r="178" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="E178" t="s">
         <v>81</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>48.329019713483547</v>
       </c>
     </row>
-    <row r="179" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="E179" t="s">
         <v>82</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>22.357138537175462</v>
       </c>
     </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="E180" t="s">
         <v>83</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>41.527307093457686</v>
       </c>
     </row>
-    <row r="181" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>6</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>20.24727046180714</v>
       </c>
     </row>
-    <row r="182" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="E182" t="s">
         <v>81</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>45.477587249429895</v>
       </c>
     </row>
-    <row r="183" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="E183" t="s">
         <v>82</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>16.901040105815941</v>
       </c>
     </row>
-    <row r="184" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="E184" t="s">
         <v>83</v>
       </c>
@@ -11815,1589 +11815,1588 @@
         <v>29.249351086591101</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A201" t="s">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>109</v>
+      </c>
+      <c r="B191" t="s">
+        <v>102</v>
+      </c>
+      <c r="C191" t="s">
+        <v>102</v>
+      </c>
+      <c r="D191" t="s">
+        <v>72</v>
+      </c>
+      <c r="E191" t="s">
+        <v>80</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <f>$AF$29</f>
+        <v>2.5</v>
+      </c>
+      <c r="N191">
+        <f>$AF$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="O191">
+        <f>(0.795 * N191) - 0.0014</f>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="Q191">
+        <f>$AF$84</f>
+        <v>90</v>
+      </c>
+      <c r="R191">
+        <f>(104.7 * O191 + 0.307 * Q191- 15) * POWER(Q191, 0.75) * 10^-3</f>
+        <v>2.188901849330922</v>
+      </c>
+      <c r="S191">
+        <f>1-EXP(-2*POWER(L191,2))</f>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T191">
+        <v>1</v>
+      </c>
+      <c r="U191">
+        <f>R191 * S191 * T191</f>
+        <v>2.1888936920529019</v>
+      </c>
+      <c r="V191">
+        <v>25</v>
+      </c>
+      <c r="W191">
+        <f>(U191 * 0.0188) + 0.00158</f>
+        <v>4.2731201410594555E-2</v>
+      </c>
+      <c r="Y191">
+        <f>$AF$4</f>
+        <v>91.25</v>
+      </c>
+      <c r="Z191">
+        <f>V191*W191*Y191</f>
+        <v>97.480553217918825</v>
+      </c>
+      <c r="AA191">
+        <f>SUM(Z191:Z214)*10^-3</f>
+        <v>1.732155183172819</v>
+      </c>
+    </row>
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="E192" t="s">
+        <v>81</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <f>$AF$30</f>
+        <v>2.5</v>
+      </c>
+      <c r="N192">
+        <f>$AF$58</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O192">
+        <f t="shared" ref="O192:O214" si="59">(0.795 * N192) - 0.0014</f>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="Q192">
+        <f>$AF$85</f>
+        <v>90</v>
+      </c>
+      <c r="R192">
+        <f>(104.7 * O192 + 0.307 * Q192- 15) * POWER(Q192, 0.75) * 10^-3</f>
+        <v>1.7024658722949466</v>
+      </c>
+      <c r="S192">
+        <f t="shared" ref="S192:S214" si="60">1-EXP(-2*POWER(L192,2))</f>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T192">
+        <v>1</v>
+      </c>
+      <c r="U192">
+        <f t="shared" ref="U192:U214" si="61">R192 * S192 * T192</f>
+        <v>1.7024595277951033</v>
+      </c>
+      <c r="V192">
+        <v>20</v>
+      </c>
+      <c r="W192">
+        <f t="shared" ref="W192:W214" si="62">(U192 * 0.0188) + 0.00158</f>
+        <v>3.3586239122547941E-2</v>
+      </c>
+      <c r="Y192">
+        <f t="shared" ref="Y192:Y214" si="63">$AF$4</f>
+        <v>91.25</v>
+      </c>
+      <c r="Z192">
+        <f t="shared" ref="Z192:Z214" si="64">V192*W192*Y192</f>
+        <v>61.294886398649993</v>
+      </c>
+    </row>
+    <row r="193" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E193" t="s">
+        <v>82</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <f>$AF$31</f>
+        <v>1.3</v>
+      </c>
+      <c r="N193">
+        <f>$AF$59</f>
+        <v>0.67</v>
+      </c>
+      <c r="O193">
+        <f t="shared" si="59"/>
+        <v>0.53125000000000011</v>
+      </c>
+      <c r="Q193">
+        <f>$AF$86</f>
+        <v>75</v>
+      </c>
+      <c r="R193">
+        <f t="shared" ref="R193:R198" si="65">(104.7 * O193 + 0.307 * Q193- 15) * POWER(Q193, 0.75) * 10^-3</f>
+        <v>1.6220828500688129</v>
+      </c>
+      <c r="S193">
+        <f t="shared" si="60"/>
+        <v>0.96595254526540064</v>
+      </c>
+      <c r="T193">
+        <v>1</v>
+      </c>
+      <c r="U193">
+        <f t="shared" si="61"/>
+        <v>1.5668550576553251</v>
+      </c>
+      <c r="V193">
+        <v>19</v>
+      </c>
+      <c r="W193">
+        <f t="shared" si="62"/>
+        <v>3.1036875083920112E-2</v>
+      </c>
+      <c r="Y193">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z193">
+        <f t="shared" si="64"/>
+        <v>53.810182176746501</v>
+      </c>
+    </row>
+    <row r="194" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E194" t="s">
+        <v>83</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <f>$AF$32</f>
+        <v>0.8</v>
+      </c>
+      <c r="N194">
+        <f>$AF$60</f>
+        <v>0.7</v>
+      </c>
+      <c r="O194">
+        <f t="shared" si="59"/>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="Q194">
+        <f>$AF$87</f>
+        <v>75</v>
+      </c>
+      <c r="R194">
+        <f t="shared" si="65"/>
+        <v>1.6857229733976102</v>
+      </c>
+      <c r="S194">
+        <f t="shared" si="60"/>
+        <v>0.72196269954680592</v>
+      </c>
+      <c r="T194">
+        <v>1</v>
+      </c>
+      <c r="U194">
+        <f t="shared" si="61"/>
+        <v>1.2170291085622071</v>
+      </c>
+      <c r="V194">
+        <v>25</v>
+      </c>
+      <c r="W194">
+        <f t="shared" si="62"/>
+        <v>2.4460147240969496E-2</v>
+      </c>
+      <c r="Y194">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z194">
+        <f t="shared" si="64"/>
+        <v>55.799710893461658</v>
+      </c>
+    </row>
+    <row r="195" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>73</v>
+      </c>
+      <c r="E195" t="s">
+        <v>80</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <f>$AG$29</f>
+        <v>2.5</v>
+      </c>
+      <c r="N195">
+        <f>$AG$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="O195">
+        <f t="shared" si="59"/>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="Q195">
+        <f>$AG$84</f>
+        <v>55</v>
+      </c>
+      <c r="R195">
+        <f t="shared" si="65"/>
+        <v>1.2959122541335131</v>
+      </c>
+      <c r="S195">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T195">
+        <v>1</v>
+      </c>
+      <c r="U195">
+        <f t="shared" si="61"/>
+        <v>1.2959074247180005</v>
+      </c>
+      <c r="V195">
+        <v>50</v>
+      </c>
+      <c r="W195">
+        <f t="shared" si="62"/>
+        <v>2.5943059584698412E-2</v>
+      </c>
+      <c r="Y195">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z195">
+        <f t="shared" si="64"/>
+        <v>118.36520935518651</v>
+      </c>
+    </row>
+    <row r="196" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E196" t="s">
+        <v>81</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <f>$AG$30</f>
+        <v>2.5</v>
+      </c>
+      <c r="N196">
+        <f>$AG$58</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O196">
+        <f t="shared" si="59"/>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="Q196">
+        <f>$AG$85</f>
+        <v>55</v>
+      </c>
+      <c r="R196">
+        <f t="shared" si="65"/>
+        <v>0.95969823125361531</v>
+      </c>
+      <c r="S196">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T196">
+        <v>1</v>
+      </c>
+      <c r="U196">
+        <f t="shared" si="61"/>
+        <v>0.95969465479115756</v>
+      </c>
+      <c r="V196">
+        <v>60</v>
+      </c>
+      <c r="W196">
+        <f t="shared" si="62"/>
+        <v>1.9622259510073764E-2</v>
+      </c>
+      <c r="Y196">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z196">
+        <f t="shared" si="64"/>
+        <v>107.43187081765385</v>
+      </c>
+    </row>
+    <row r="197" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E197" t="s">
+        <v>82</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <f>$AG$31</f>
+        <v>1.3</v>
+      </c>
+      <c r="N197">
+        <f>$AG$59</f>
+        <v>0.67</v>
+      </c>
+      <c r="O197">
+        <f t="shared" si="59"/>
+        <v>0.53125000000000011</v>
+      </c>
+      <c r="Q197">
+        <f>$AG$86</f>
+        <v>50</v>
+      </c>
+      <c r="R197">
+        <f t="shared" si="65"/>
+        <v>1.052440031254225</v>
+      </c>
+      <c r="S197">
+        <f t="shared" si="60"/>
+        <v>0.96595254526540064</v>
+      </c>
+      <c r="T197">
+        <v>1</v>
+      </c>
+      <c r="U197">
+        <f t="shared" si="61"/>
+        <v>1.0166071269292165</v>
+      </c>
+      <c r="V197">
+        <v>55</v>
+      </c>
+      <c r="W197">
+        <f t="shared" si="62"/>
+        <v>2.0692213986269272E-2</v>
+      </c>
+      <c r="Y197">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z197">
+        <f t="shared" si="64"/>
+        <v>103.8490489435889</v>
+      </c>
+    </row>
+    <row r="198" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E198" t="s">
+        <v>83</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <f>$AG$32</f>
+        <v>0.8</v>
+      </c>
+      <c r="N198">
+        <f>$AG$60</f>
+        <v>0.7</v>
+      </c>
+      <c r="O198">
+        <f t="shared" si="59"/>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="Q198">
+        <f>$AG$87</f>
+        <v>45</v>
+      </c>
+      <c r="R198">
+        <f t="shared" si="65"/>
+        <v>0.98919258792655118</v>
+      </c>
+      <c r="S198">
+        <f t="shared" si="60"/>
+        <v>0.72196269954680592</v>
+      </c>
+      <c r="T198">
+        <v>1</v>
+      </c>
+      <c r="U198">
+        <f t="shared" si="61"/>
+        <v>0.71416015115114406</v>
+      </c>
+      <c r="V198">
+        <v>55</v>
+      </c>
+      <c r="W198">
+        <f t="shared" si="62"/>
+        <v>1.5006210841641509E-2</v>
+      </c>
+      <c r="Y198">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z198">
+        <f t="shared" si="64"/>
+        <v>75.312420661488332</v>
+      </c>
+    </row>
+    <row r="199" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>3</v>
+      </c>
+      <c r="D199" t="s">
+        <v>74</v>
+      </c>
+      <c r="E199" t="s">
+        <v>80</v>
+      </c>
+      <c r="G199">
+        <v>80</v>
+      </c>
+      <c r="H199">
+        <v>87</v>
+      </c>
+      <c r="I199">
+        <f>(G199/100*MIN(H199,100)/100)</f>
+        <v>0.69600000000000006</v>
+      </c>
+      <c r="J199">
+        <f>$AF$3</f>
+        <v>1.3</v>
+      </c>
+      <c r="L199">
+        <f>$AH$29</f>
+        <v>2.5</v>
+      </c>
+      <c r="N199">
+        <f>$AH$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="O199">
+        <f t="shared" si="59"/>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="Q199">
+        <f>$AH$84</f>
+        <v>45</v>
+      </c>
+      <c r="R199">
+        <f>(104.7 * O199 + 0.307 * Q199- 15) * POWER(Q199, 0.75) * 10^-3</f>
+        <v>1.0615017285371116</v>
+      </c>
+      <c r="S199">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T199">
+        <f>(I199 * J199) + (1 - I199)</f>
+        <v>1.2088000000000001</v>
+      </c>
+      <c r="U199">
+        <f t="shared" si="61"/>
+        <v>1.2831385076256505</v>
+      </c>
+      <c r="V199">
+        <v>60</v>
+      </c>
+      <c r="W199">
+        <f t="shared" si="62"/>
+        <v>2.5703003943362231E-2</v>
+      </c>
+      <c r="Y199">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z199">
+        <f t="shared" si="64"/>
+        <v>140.72394658990822</v>
+      </c>
+    </row>
+    <row r="200" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E200" t="s">
+        <v>81</v>
+      </c>
+      <c r="G200">
+        <v>10</v>
+      </c>
+      <c r="H200">
+        <v>8</v>
+      </c>
+      <c r="I200">
+        <f>(G200/100*MIN(H200,100)/100)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J200">
+        <f>$AF$3</f>
+        <v>1.3</v>
+      </c>
+      <c r="L200">
+        <f>$AH$30</f>
+        <v>2.5</v>
+      </c>
+      <c r="N200">
+        <f>$AH$58</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O200">
+        <f t="shared" si="59"/>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="Q200">
+        <f>$AH$85</f>
+        <v>45</v>
+      </c>
+      <c r="R200">
+        <f t="shared" ref="R200:R214" si="66">(104.7 * O200 + 0.307 * Q200- 15) * POWER(Q200, 0.75) * 10^-3</f>
+        <v>0.77226516609487061</v>
+      </c>
+      <c r="S200">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T200">
+        <f t="shared" ref="T200:T206" si="67">(I200 * J200) + (1 - I200)</f>
+        <v>1.0024</v>
+      </c>
+      <c r="U200">
+        <f t="shared" si="61"/>
+        <v>0.77411571762195275</v>
+      </c>
+      <c r="V200">
+        <v>70</v>
+      </c>
+      <c r="W200">
+        <f t="shared" si="62"/>
+        <v>1.6133375491292713E-2</v>
+      </c>
+      <c r="Y200">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z200">
+        <f t="shared" si="64"/>
+        <v>103.05193595063221</v>
+      </c>
+    </row>
+    <row r="201" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E201" t="s">
+        <v>82</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <f t="shared" ref="I201:I204" si="68">(G201/100*MIN(H201,100)/100)</f>
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <f>$AH$31</f>
+        <v>1.3</v>
+      </c>
+      <c r="N201">
+        <f>$AH$59</f>
+        <v>0.67</v>
+      </c>
+      <c r="O201">
+        <f t="shared" si="59"/>
+        <v>0.53125000000000011</v>
+      </c>
+      <c r="Q201">
+        <f>$AH$86</f>
+        <v>45</v>
+      </c>
+      <c r="R201">
+        <f t="shared" si="66"/>
+        <v>0.94580710356021536</v>
+      </c>
+      <c r="S201">
+        <f t="shared" si="60"/>
+        <v>0.96595254526540064</v>
+      </c>
+      <c r="T201">
+        <f t="shared" si="67"/>
+        <v>1</v>
+      </c>
+      <c r="U201">
+        <f t="shared" si="61"/>
+        <v>0.91360477901408643</v>
+      </c>
+      <c r="V201">
+        <v>60</v>
+      </c>
+      <c r="W201">
+        <f t="shared" si="62"/>
+        <v>1.8755769845464829E-2</v>
+      </c>
+      <c r="Y201">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z201">
+        <f t="shared" si="64"/>
+        <v>102.68783990391994</v>
+      </c>
+    </row>
+    <row r="202" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E202" t="s">
+        <v>83</v>
+      </c>
+      <c r="G202">
+        <v>5</v>
+      </c>
+      <c r="H202">
+        <v>4</v>
+      </c>
+      <c r="I202">
+        <f t="shared" si="68"/>
+        <v>2E-3</v>
+      </c>
+      <c r="J202">
+        <f>$AF$3</f>
+        <v>1.3</v>
+      </c>
+      <c r="L202">
+        <f>$AH$32</f>
+        <v>0.8</v>
+      </c>
+      <c r="N202">
+        <f>$AH$60</f>
+        <v>0.7</v>
+      </c>
+      <c r="O202">
+        <f t="shared" si="59"/>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="Q202">
+        <f>$AH$87</f>
+        <v>50</v>
+      </c>
+      <c r="R202">
+        <f t="shared" si="66"/>
+        <v>1.0993929471578776</v>
+      </c>
+      <c r="S202">
+        <f t="shared" si="60"/>
+        <v>0.72196269954680592</v>
+      </c>
+      <c r="T202">
+        <f t="shared" si="67"/>
+        <v>1.0005999999999999</v>
+      </c>
+      <c r="U202">
+        <f t="shared" si="61"/>
+        <v>0.79419693241281586</v>
+      </c>
+      <c r="V202">
+        <v>50</v>
+      </c>
+      <c r="W202">
+        <f t="shared" si="62"/>
+        <v>1.6510902329360939E-2</v>
+      </c>
+      <c r="Y202">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z202">
+        <f t="shared" si="64"/>
+        <v>75.33099187770928</v>
+      </c>
+    </row>
+    <row r="203" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>4</v>
+      </c>
+      <c r="D203" t="s">
+        <v>75</v>
+      </c>
+      <c r="E203" t="s">
+        <v>80</v>
+      </c>
+      <c r="G203">
+        <v>90</v>
+      </c>
+      <c r="H203">
+        <v>87</v>
+      </c>
+      <c r="I203">
+        <f t="shared" si="68"/>
+        <v>0.78299999999999992</v>
+      </c>
+      <c r="J203">
+        <f>$AF$3</f>
+        <v>1.3</v>
+      </c>
+      <c r="L203">
+        <f>$AI$29</f>
+        <v>2.5</v>
+      </c>
+      <c r="N203">
+        <f>$AI$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="O203">
+        <f t="shared" si="59"/>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="Q203">
+        <f>$AI$84</f>
+        <v>50</v>
+      </c>
+      <c r="R203">
+        <f t="shared" si="66"/>
+        <v>1.1776478069972991</v>
+      </c>
+      <c r="S203">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T203">
+        <f t="shared" si="67"/>
+        <v>1.2349000000000001</v>
+      </c>
+      <c r="U203">
+        <f t="shared" si="61"/>
+        <v>1.4542718572739379</v>
+      </c>
+      <c r="V203">
+        <v>40</v>
+      </c>
+      <c r="W203">
+        <f t="shared" si="62"/>
+        <v>2.8920310916750035E-2</v>
+      </c>
+      <c r="Y203">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z203">
+        <f t="shared" si="64"/>
+        <v>105.55913484613764</v>
+      </c>
+    </row>
+    <row r="204" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E204" t="s">
+        <v>81</v>
+      </c>
+      <c r="G204">
+        <v>5</v>
+      </c>
+      <c r="H204">
+        <v>3</v>
+      </c>
+      <c r="I204">
+        <f t="shared" si="68"/>
+        <v>1.5000000000000002E-3</v>
+      </c>
+      <c r="J204">
+        <f>$AF$3</f>
+        <v>1.3</v>
+      </c>
+      <c r="L204">
+        <f>$AI$30</f>
+        <v>2.5</v>
+      </c>
+      <c r="N204">
+        <f>$AI$58</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O204">
+        <f t="shared" si="59"/>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="Q204">
+        <f>$AI$85</f>
+        <v>50</v>
+      </c>
+      <c r="R204">
+        <f t="shared" si="66"/>
+        <v>0.8646283676396137</v>
+      </c>
+      <c r="S204">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T204">
+        <f t="shared" si="67"/>
+        <v>1.0004500000000001</v>
+      </c>
+      <c r="U204">
+        <f t="shared" si="61"/>
+        <v>0.86501422678502615</v>
+      </c>
+      <c r="V204">
+        <v>45</v>
+      </c>
+      <c r="W204">
+        <f t="shared" si="62"/>
+        <v>1.7842267463558492E-2</v>
+      </c>
+      <c r="Y204">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z204">
+        <f t="shared" si="64"/>
+        <v>73.26481077223707</v>
+      </c>
+    </row>
+    <row r="205" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E205" t="s">
+        <v>82</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <f>$AI$31</f>
+        <v>1.3</v>
+      </c>
+      <c r="N205">
+        <f>$AI$59</f>
+        <v>0.67</v>
+      </c>
+      <c r="O205">
+        <f t="shared" si="59"/>
+        <v>0.53125000000000011</v>
+      </c>
+      <c r="Q205">
+        <f>$AI$86</f>
+        <v>50</v>
+      </c>
+      <c r="R205">
+        <f t="shared" si="66"/>
+        <v>1.052440031254225</v>
+      </c>
+      <c r="S205">
+        <f t="shared" si="60"/>
+        <v>0.96595254526540064</v>
+      </c>
+      <c r="T205">
+        <f t="shared" si="67"/>
+        <v>1</v>
+      </c>
+      <c r="U205">
+        <f t="shared" si="61"/>
+        <v>1.0166071269292165</v>
+      </c>
+      <c r="V205">
+        <v>40</v>
+      </c>
+      <c r="W205">
+        <f t="shared" si="62"/>
+        <v>2.0692213986269272E-2</v>
+      </c>
+      <c r="Y205">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z205">
+        <f t="shared" si="64"/>
+        <v>75.52658104988285</v>
+      </c>
+    </row>
+    <row r="206" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E206" t="s">
+        <v>83</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <f>$AI$32</f>
+        <v>0.8</v>
+      </c>
+      <c r="N206">
+        <f>$AI$60</f>
+        <v>0.7</v>
+      </c>
+      <c r="O206">
+        <f t="shared" si="59"/>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="Q206">
+        <f>$AI$87</f>
+        <v>55</v>
+      </c>
+      <c r="R206">
+        <f t="shared" si="66"/>
+        <v>1.2118587484135388</v>
+      </c>
+      <c r="S206">
+        <f t="shared" si="60"/>
+        <v>0.72196269954680592</v>
+      </c>
+      <c r="T206">
+        <f t="shared" si="67"/>
+        <v>1</v>
+      </c>
+      <c r="U206">
+        <f t="shared" si="61"/>
+        <v>0.87491681347405192</v>
+      </c>
+      <c r="V206">
+        <v>35</v>
+      </c>
+      <c r="W206">
+        <f t="shared" si="62"/>
+        <v>1.8028436093312179E-2</v>
+      </c>
+      <c r="Y206">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z206">
+        <f t="shared" si="64"/>
+        <v>57.578317773015769</v>
+      </c>
+    </row>
+    <row r="207" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>5</v>
+      </c>
+      <c r="D207" t="s">
+        <v>76</v>
+      </c>
+      <c r="E207" t="s">
+        <v>80</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <f>$AJ$29</f>
+        <v>2.5</v>
+      </c>
+      <c r="N207">
+        <f>$AJ$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="O207">
+        <f t="shared" si="59"/>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="Q207">
+        <f>$AJ$84</f>
+        <v>50</v>
+      </c>
+      <c r="R207">
+        <f t="shared" si="66"/>
+        <v>1.1776478069972991</v>
+      </c>
+      <c r="S207">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="U207">
+        <f t="shared" si="61"/>
+        <v>1.1776434183123636</v>
+      </c>
+      <c r="V207">
+        <v>25</v>
+      </c>
+      <c r="W207">
+        <f t="shared" si="62"/>
+        <v>2.3719696264272439E-2</v>
+      </c>
+      <c r="Y207">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z207">
+        <f t="shared" si="64"/>
+        <v>54.110557102871503</v>
+      </c>
+    </row>
+    <row r="208" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E208" t="s">
+        <v>81</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <f>$AJ$30</f>
+        <v>2.5</v>
+      </c>
+      <c r="N208">
+        <f>$AJ$58</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O208">
+        <f t="shared" si="59"/>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="Q208">
+        <f>$AJ$85</f>
+        <v>50</v>
+      </c>
+      <c r="R208">
+        <f t="shared" si="66"/>
+        <v>0.8646283676396137</v>
+      </c>
+      <c r="S208">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="U208">
+        <f t="shared" si="61"/>
+        <v>0.86462514546956482</v>
+      </c>
+      <c r="V208">
+        <v>30</v>
+      </c>
+      <c r="W208">
+        <f t="shared" si="62"/>
+        <v>1.7834952734827821E-2</v>
+      </c>
+      <c r="Y208">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z208">
+        <f t="shared" si="64"/>
+        <v>48.823183111591163</v>
+      </c>
+    </row>
+    <row r="209" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E209" t="s">
+        <v>82</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <f>$AJ$31</f>
+        <v>1.3</v>
+      </c>
+      <c r="N209">
+        <f>$AJ$59</f>
+        <v>0.67</v>
+      </c>
+      <c r="O209">
+        <f t="shared" si="59"/>
+        <v>0.53125000000000011</v>
+      </c>
+      <c r="Q209">
+        <f>$AJ$86</f>
+        <v>50</v>
+      </c>
+      <c r="R209">
+        <f t="shared" si="66"/>
+        <v>1.052440031254225</v>
+      </c>
+      <c r="S209">
+        <f t="shared" si="60"/>
+        <v>0.96595254526540064</v>
+      </c>
+      <c r="T209">
+        <v>1</v>
+      </c>
+      <c r="U209">
+        <f t="shared" si="61"/>
+        <v>1.0166071269292165</v>
+      </c>
+      <c r="V209">
+        <v>25</v>
+      </c>
+      <c r="W209">
+        <f t="shared" si="62"/>
+        <v>2.0692213986269272E-2</v>
+      </c>
+      <c r="Y209">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z209">
+        <f t="shared" si="64"/>
+        <v>47.204113156176774</v>
+      </c>
+    </row>
+    <row r="210" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E210" t="s">
+        <v>83</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <f>$AJ$32</f>
+        <v>0.8</v>
+      </c>
+      <c r="N210">
+        <f>$AJ$60</f>
+        <v>0.7</v>
+      </c>
+      <c r="O210">
+        <f t="shared" si="59"/>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="Q210">
+        <f>$AJ$87</f>
+        <v>50</v>
+      </c>
+      <c r="R210">
+        <f t="shared" si="66"/>
+        <v>1.0993929471578776</v>
+      </c>
+      <c r="S210">
+        <f t="shared" si="60"/>
+        <v>0.72196269954680592</v>
+      </c>
+      <c r="T210">
+        <v>1</v>
+      </c>
+      <c r="U210">
+        <f t="shared" si="61"/>
+        <v>0.79372069999282024</v>
+      </c>
+      <c r="V210">
+        <v>20</v>
+      </c>
+      <c r="W210">
+        <f t="shared" si="62"/>
+        <v>1.6501949159865022E-2</v>
+      </c>
+      <c r="Y210">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z210">
+        <f t="shared" si="64"/>
+        <v>30.116057216753667</v>
+      </c>
+    </row>
+    <row r="211" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>6</v>
+      </c>
+      <c r="D211" t="s">
+        <v>77</v>
+      </c>
+      <c r="E211" t="s">
+        <v>80</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <f>$AK$29</f>
+        <v>2.5</v>
+      </c>
+      <c r="N211">
+        <f>$AK$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="O211">
+        <f t="shared" si="59"/>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="Q211">
+        <f>$AK$84</f>
+        <v>14</v>
+      </c>
+      <c r="R211">
+        <f t="shared" si="66"/>
+        <v>0.3733079325984448</v>
+      </c>
+      <c r="S211">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T211">
+        <v>1</v>
+      </c>
+      <c r="U211">
+        <f t="shared" si="61"/>
+        <v>0.37330654140925362</v>
+      </c>
+      <c r="V211">
+        <v>15</v>
+      </c>
+      <c r="W211">
+        <f t="shared" si="62"/>
+        <v>8.5981629784939693E-3</v>
+      </c>
+      <c r="Y211">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z211">
+        <f t="shared" si="64"/>
+        <v>11.76873557681362</v>
+      </c>
+    </row>
+    <row r="212" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E212" t="s">
+        <v>81</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <f>$AK$30</f>
+        <v>2.5</v>
+      </c>
+      <c r="N212">
+        <f>$AK$58</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O212">
+        <f t="shared" si="59"/>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="Q212">
+        <f>$AK$85</f>
+        <v>24</v>
+      </c>
+      <c r="R212">
+        <f t="shared" si="66"/>
+        <v>0.41205872426603418</v>
+      </c>
+      <c r="S212">
+        <f t="shared" si="60"/>
+        <v>0.99999627334682795</v>
+      </c>
+      <c r="T212">
+        <v>1</v>
+      </c>
+      <c r="U212">
+        <f t="shared" si="61"/>
+        <v>0.41205718866608232</v>
+      </c>
+      <c r="V212">
+        <v>45</v>
+      </c>
+      <c r="W212">
+        <f t="shared" si="62"/>
+        <v>9.3266751469223488E-3</v>
+      </c>
+      <c r="Y212">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z212">
+        <f t="shared" si="64"/>
+        <v>38.297659822049894</v>
+      </c>
+    </row>
+    <row r="213" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E213" t="s">
+        <v>82</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <f>$AK$31</f>
+        <v>1.3</v>
+      </c>
+      <c r="N213">
+        <f>$AK$59</f>
+        <v>0.67</v>
+      </c>
+      <c r="O213">
+        <f t="shared" si="59"/>
+        <v>0.53125000000000011</v>
+      </c>
+      <c r="Q213">
+        <f>$AK$86</f>
+        <v>36</v>
+      </c>
+      <c r="R213">
+        <f t="shared" si="66"/>
+        <v>0.75944776069416087</v>
+      </c>
+      <c r="S213">
+        <f t="shared" si="60"/>
+        <v>0.96595254526540064</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <f t="shared" si="61"/>
+        <v>0.73359049743863358</v>
+      </c>
+      <c r="V213">
+        <v>40</v>
+      </c>
+      <c r="W213">
+        <f t="shared" si="62"/>
+        <v>1.5371501351846312E-2</v>
+      </c>
+      <c r="Y213">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z213">
+        <f t="shared" si="64"/>
+        <v>56.105979934239038</v>
+      </c>
+    </row>
+    <row r="214" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E214" t="s">
+        <v>83</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <f>$AK$32</f>
+        <v>0.8</v>
+      </c>
+      <c r="N214">
+        <f>$AK$60</f>
+        <v>0.7</v>
+      </c>
+      <c r="O214">
+        <f t="shared" si="59"/>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="Q214">
+        <f>$AK$87</f>
+        <v>42</v>
+      </c>
+      <c r="R214">
+        <f t="shared" si="66"/>
+        <v>0.92411404077093851</v>
+      </c>
+      <c r="S214">
+        <f t="shared" si="60"/>
+        <v>0.72196269954680592</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <f t="shared" si="61"/>
+        <v>0.66717586756409386</v>
+      </c>
+      <c r="V214">
+        <v>30</v>
+      </c>
+      <c r="W214">
+        <f t="shared" si="62"/>
+        <v>1.4122906310204965E-2</v>
+      </c>
+      <c r="Y214">
+        <f t="shared" si="63"/>
+        <v>91.25</v>
+      </c>
+      <c r="Z214">
+        <f t="shared" si="64"/>
+        <v>38.661456024186094</v>
+      </c>
+    </row>
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
         <v>108</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B231" t="s">
         <v>126</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C231" t="s">
         <v>85</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D231" t="s">
         <v>72</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E231" t="s">
         <v>80</v>
       </c>
-      <c r="G201">
-        <v>0</v>
-      </c>
-      <c r="H201">
-        <v>0</v>
-      </c>
-      <c r="I201">
-        <v>0</v>
-      </c>
-      <c r="L201">
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="L231">
         <f>$AF$17</f>
         <v>2.9</v>
       </c>
-      <c r="N201">
+      <c r="N231">
         <f>$AF$45</f>
         <v>0.75</v>
       </c>
-      <c r="O201">
-        <f>(0.795 * N201) - 0.0014</f>
+      <c r="O231">
+        <f>(0.795 * N231) - 0.0014</f>
         <v>0.5948500000000001</v>
       </c>
-      <c r="Q201">
+      <c r="Q231">
         <f>$AF$72</f>
         <v>75</v>
       </c>
-      <c r="R201">
-        <f>(104.7 * O201 + 0.307 * Q201- 15) * POWER(Q201, 0.75) * 10^-3</f>
-        <v>1.7917898456122741</v>
-      </c>
-      <c r="S201">
-        <f>1-EXP(-2*POWER(L201,2))</f>
-        <v>0.9999999504359468</v>
-      </c>
-      <c r="T201">
-        <v>1</v>
-      </c>
-      <c r="U201">
-        <f>R201 * S201 * T201</f>
-        <v>1.7917897568039067</v>
-      </c>
-      <c r="V201">
-        <v>50</v>
-      </c>
-      <c r="W201">
-        <f>(U201 * 0.0188) + 0.00158</f>
-        <v>3.5265647427913445E-2</v>
-      </c>
-      <c r="Y201">
-        <f>$AF$4</f>
-        <v>91.25</v>
-      </c>
-      <c r="Z201">
-        <f>V201*W201*Y201</f>
-        <v>160.89951638985508</v>
-      </c>
-      <c r="AA201">
-        <f>SUM(Z201:Z224)*10^-3</f>
-        <v>3.7710363373989564</v>
-      </c>
-    </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="E202" t="s">
-        <v>81</v>
-      </c>
-      <c r="G202">
-        <v>0</v>
-      </c>
-      <c r="H202">
-        <v>0</v>
-      </c>
-      <c r="I202">
-        <v>0</v>
-      </c>
-      <c r="L202">
-        <f>$AF$18</f>
-        <v>2.5</v>
-      </c>
-      <c r="N202">
-        <f>$AF$46</f>
-        <v>0.61</v>
-      </c>
-      <c r="O202">
-        <f t="shared" ref="O202:O224" si="59">(0.795 * N202) - 0.0014</f>
-        <v>0.48354999999999998</v>
-      </c>
-      <c r="Q202">
-        <f>$AF$73</f>
-        <v>75</v>
-      </c>
-      <c r="R202">
-        <f>(104.7 * O202 + 0.307 * Q202- 15) * POWER(Q202, 0.75) * 10^-3</f>
-        <v>1.4948026034112167</v>
-      </c>
-      <c r="S202">
-        <f t="shared" ref="S202:S224" si="60">1-EXP(-2*POWER(L202,2))</f>
-        <v>0.99999627334682795</v>
-      </c>
-      <c r="T202">
-        <v>1</v>
-      </c>
-      <c r="U202">
-        <f t="shared" ref="U202:U224" si="61">R202 * S202 * T202</f>
-        <v>1.494797032800353</v>
-      </c>
-      <c r="V202">
-        <v>40</v>
-      </c>
-      <c r="W202">
-        <f t="shared" ref="W202:W224" si="62">(U202 * 0.0188) + 0.00158</f>
-        <v>2.9682184216646638E-2</v>
-      </c>
-      <c r="Y202">
-        <f t="shared" ref="Y202:Y224" si="63">$AF$4</f>
-        <v>91.25</v>
-      </c>
-      <c r="Z202">
-        <f t="shared" ref="Z202:Z224" si="64">V202*W202*Y202</f>
-        <v>108.33997239076024</v>
-      </c>
-    </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="E203" t="s">
-        <v>82</v>
-      </c>
-      <c r="G203">
-        <v>0</v>
-      </c>
-      <c r="H203">
-        <v>0</v>
-      </c>
-      <c r="I203">
-        <v>0</v>
-      </c>
-      <c r="L203">
-        <f>$AF$19</f>
-        <v>1.6</v>
-      </c>
-      <c r="N203">
-        <f>$AF$47</f>
-        <v>0.64</v>
-      </c>
-      <c r="O203">
-        <f t="shared" si="59"/>
-        <v>0.50740000000000007</v>
-      </c>
-      <c r="Q203">
-        <f>$AF$74</f>
-        <v>69</v>
-      </c>
-      <c r="R203">
-        <f t="shared" ref="R203:R208" si="65">(104.7 * O203 + 0.307 * Q203- 15) * POWER(Q203, 0.75) * 10^-3</f>
-        <v>1.4198696820048529</v>
-      </c>
-      <c r="S203">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T203">
-        <v>1</v>
-      </c>
-      <c r="U203">
-        <f t="shared" si="61"/>
-        <v>1.4113845082772669</v>
-      </c>
-      <c r="V203">
-        <v>38</v>
-      </c>
-      <c r="W203">
-        <f t="shared" si="62"/>
-        <v>2.811402875561262E-2</v>
-      </c>
-      <c r="Y203">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z203">
-        <f t="shared" si="64"/>
-        <v>97.485394710086752</v>
-      </c>
-    </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="E204" t="s">
-        <v>83</v>
-      </c>
-      <c r="G204">
-        <v>0</v>
-      </c>
-      <c r="H204">
-        <v>0</v>
-      </c>
-      <c r="I204">
-        <v>0</v>
-      </c>
-      <c r="K204" s="2">
-        <v>1.9</v>
-      </c>
-      <c r="L204" s="2">
-        <v>1.9</v>
-      </c>
-      <c r="N204">
-        <f>$AF$48</f>
-        <v>0.72</v>
-      </c>
-      <c r="O204">
-        <f t="shared" si="59"/>
-        <v>0.57100000000000006</v>
-      </c>
-      <c r="Q204">
-        <f>$AF$75</f>
-        <v>69</v>
-      </c>
-      <c r="R204">
-        <f t="shared" si="65"/>
-        <v>1.5792888783210146</v>
-      </c>
-      <c r="S204">
-        <f t="shared" si="60"/>
-        <v>0.99926819758111951</v>
-      </c>
-      <c r="T204">
-        <v>1</v>
-      </c>
-      <c r="U204">
-        <f t="shared" si="61"/>
-        <v>1.5781331508997483</v>
-      </c>
-      <c r="V204">
-        <v>50</v>
-      </c>
-      <c r="W204">
-        <f t="shared" si="62"/>
-        <v>3.124890323691527E-2</v>
-      </c>
-      <c r="Y204">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z204">
-        <f t="shared" si="64"/>
-        <v>142.57312101842592</v>
-      </c>
-    </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A205">
-        <v>2</v>
-      </c>
-      <c r="D205" t="s">
-        <v>73</v>
-      </c>
-      <c r="E205" t="s">
-        <v>80</v>
-      </c>
-      <c r="G205">
-        <v>0</v>
-      </c>
-      <c r="H205">
-        <v>0</v>
-      </c>
-      <c r="I205">
-        <v>0</v>
-      </c>
-      <c r="L205">
-        <f>$AG$17</f>
-        <v>2.9</v>
-      </c>
-      <c r="N205">
-        <f>$AG$45</f>
-        <v>0.75</v>
-      </c>
-      <c r="O205">
-        <f t="shared" si="59"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q205">
-        <f>$AG$72</f>
-        <v>62</v>
-      </c>
-      <c r="R205">
-        <f t="shared" si="65"/>
-        <v>1.4652245899459331</v>
-      </c>
-      <c r="S205">
-        <f t="shared" si="60"/>
-        <v>0.9999999504359468</v>
-      </c>
-      <c r="T205">
-        <v>1</v>
-      </c>
-      <c r="U205">
-        <f t="shared" si="61"/>
-        <v>1.4652245173234635</v>
-      </c>
-      <c r="V205">
-        <v>100</v>
-      </c>
-      <c r="W205">
-        <f t="shared" si="62"/>
-        <v>2.9126220925681116E-2</v>
-      </c>
-      <c r="Y205">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z205">
-        <f t="shared" si="64"/>
-        <v>265.77676594684021</v>
-      </c>
-    </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="E206" t="s">
-        <v>81</v>
-      </c>
-      <c r="G206">
-        <v>0</v>
-      </c>
-      <c r="H206">
-        <v>0</v>
-      </c>
-      <c r="I206">
-        <v>0</v>
-      </c>
-      <c r="L206">
-        <f>$AG$18</f>
-        <v>2.5</v>
-      </c>
-      <c r="N206">
-        <f>$AG$46</f>
-        <v>0.61</v>
-      </c>
-      <c r="O206">
-        <f t="shared" si="59"/>
-        <v>0.48354999999999998</v>
-      </c>
-      <c r="Q206">
-        <f>$AG$73</f>
-        <v>55</v>
-      </c>
-      <c r="R206">
-        <f t="shared" si="65"/>
-        <v>1.0605624381175847</v>
-      </c>
-      <c r="S206">
-        <f t="shared" si="60"/>
-        <v>0.99999627334682795</v>
-      </c>
-      <c r="T206">
-        <v>1</v>
-      </c>
-      <c r="U206">
-        <f t="shared" si="61"/>
-        <v>1.0605584857692105</v>
-      </c>
-      <c r="V206">
-        <v>120</v>
-      </c>
-      <c r="W206">
-        <f t="shared" si="62"/>
-        <v>2.1518499532461158E-2</v>
-      </c>
-      <c r="Y206">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z206">
-        <f t="shared" si="64"/>
-        <v>235.6275698804497</v>
-      </c>
-    </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="E207" t="s">
-        <v>82</v>
-      </c>
-      <c r="G207">
-        <v>0</v>
-      </c>
-      <c r="H207">
-        <v>0</v>
-      </c>
-      <c r="I207">
-        <v>0</v>
-      </c>
-      <c r="L207">
-        <f>$AG$19</f>
-        <v>1.6</v>
-      </c>
-      <c r="N207">
-        <f>$AG$47</f>
-        <v>0.64</v>
-      </c>
-      <c r="O207">
-        <f t="shared" si="59"/>
-        <v>0.50740000000000007</v>
-      </c>
-      <c r="Q207">
-        <f>$AG$74</f>
-        <v>55</v>
-      </c>
-      <c r="R207">
-        <f t="shared" si="65"/>
-        <v>1.1109945415495692</v>
-      </c>
-      <c r="S207">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T207">
-        <v>1</v>
-      </c>
-      <c r="U207">
-        <f t="shared" si="61"/>
-        <v>1.1043552127330423</v>
-      </c>
-      <c r="V207">
-        <v>115</v>
-      </c>
-      <c r="W207">
-        <f t="shared" si="62"/>
-        <v>2.2341877999381195E-2</v>
-      </c>
-      <c r="Y207">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z207">
-        <f t="shared" si="64"/>
-        <v>234.4500822560064</v>
-      </c>
-    </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="E208" t="s">
-        <v>83</v>
-      </c>
-      <c r="G208">
-        <v>0</v>
-      </c>
-      <c r="H208">
-        <v>0</v>
-      </c>
-      <c r="I208">
-        <v>0</v>
-      </c>
-      <c r="K208" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="L208" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="N208">
-        <f>$AG$48</f>
-        <v>0.72</v>
-      </c>
-      <c r="O208">
-        <f t="shared" si="59"/>
-        <v>0.57100000000000006</v>
-      </c>
-      <c r="Q208">
-        <f>$AG$75</f>
-        <v>55</v>
-      </c>
-      <c r="R208">
-        <f t="shared" si="65"/>
-        <v>1.2454801507015281</v>
-      </c>
-      <c r="S208">
-        <f t="shared" si="60"/>
-        <v>0.99846618932067555</v>
-      </c>
-      <c r="T208">
-        <v>1</v>
-      </c>
-      <c r="U208">
-        <f t="shared" si="61"/>
-        <v>1.2435698199454954</v>
-      </c>
-      <c r="V208">
-        <v>110</v>
-      </c>
-      <c r="W208">
-        <f t="shared" si="62"/>
-        <v>2.4959112614975316E-2</v>
-      </c>
-      <c r="Y208">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z208">
-        <f t="shared" si="64"/>
-        <v>250.52709287281473</v>
-      </c>
-    </row>
-    <row r="209" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A209">
-        <v>3</v>
-      </c>
-      <c r="D209" t="s">
-        <v>74</v>
-      </c>
-      <c r="E209" t="s">
-        <v>80</v>
-      </c>
-      <c r="G209">
-        <v>90</v>
-      </c>
-      <c r="H209">
-        <v>85</v>
-      </c>
-      <c r="I209">
-        <f>(G209/100*MIN(H209,100)/100)</f>
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="J209">
-        <f>$AF$3</f>
-        <v>1.3</v>
-      </c>
-      <c r="L209">
-        <f>$AH$17</f>
-        <v>2.9</v>
-      </c>
-      <c r="N209">
-        <f>$AH$45</f>
-        <v>0.75</v>
-      </c>
-      <c r="O209">
-        <f t="shared" si="59"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q209">
-        <f>$AH$72</f>
-        <v>44</v>
-      </c>
-      <c r="R209">
-        <f>(104.7 * O209 + 0.307 * Q209- 15) * POWER(Q209, 0.75) * 10^-3</f>
-        <v>1.0385156413271623</v>
-      </c>
-      <c r="S209">
-        <f t="shared" si="60"/>
-        <v>0.9999999504359468</v>
-      </c>
-      <c r="T209">
-        <f>(I209 * J209) + (1 - I209)</f>
-        <v>1.2295</v>
-      </c>
-      <c r="U209">
-        <f t="shared" si="61"/>
-        <v>1.2768549177256379</v>
-      </c>
-      <c r="V209">
-        <v>120</v>
-      </c>
-      <c r="W209">
-        <f t="shared" si="62"/>
-        <v>2.5584872453241994E-2</v>
-      </c>
-      <c r="Y209">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z209">
-        <f t="shared" si="64"/>
-        <v>280.15435336299987</v>
-      </c>
-    </row>
-    <row r="210" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E210" t="s">
-        <v>81</v>
-      </c>
-      <c r="G210">
-        <v>0</v>
-      </c>
-      <c r="H210">
-        <v>0</v>
-      </c>
-      <c r="I210">
-        <f>(G210/100*MIN(H210,100)/100)</f>
-        <v>0</v>
-      </c>
-      <c r="L210">
-        <f>$AH$18</f>
-        <v>2.5</v>
-      </c>
-      <c r="N210">
-        <f>$AH$46</f>
-        <v>0.61</v>
-      </c>
-      <c r="O210">
-        <f t="shared" si="59"/>
-        <v>0.48354999999999998</v>
-      </c>
-      <c r="Q210">
-        <f>$AH$73</f>
-        <v>42</v>
-      </c>
-      <c r="R210">
-        <f t="shared" ref="R210:R224" si="66">(104.7 * O210 + 0.307 * Q210- 15) * POWER(Q210, 0.75) * 10^-3</f>
-        <v>0.80052120768394575</v>
-      </c>
-      <c r="S210">
-        <f t="shared" si="60"/>
-        <v>0.99999627334682795</v>
-      </c>
-      <c r="T210">
-        <f t="shared" ref="T210:T216" si="67">(I210 * J210) + (1 - I210)</f>
-        <v>1</v>
-      </c>
-      <c r="U210">
-        <f t="shared" si="61"/>
-        <v>0.80051822441904785</v>
-      </c>
-      <c r="V210">
-        <v>130</v>
-      </c>
-      <c r="W210">
-        <f t="shared" si="62"/>
-        <v>1.6629742619078101E-2</v>
-      </c>
-      <c r="Y210">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z210">
-        <f t="shared" si="64"/>
-        <v>197.27032181881395</v>
-      </c>
-    </row>
-    <row r="211" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E211" t="s">
-        <v>82</v>
-      </c>
-      <c r="G211">
-        <v>0</v>
-      </c>
-      <c r="H211">
-        <v>0</v>
-      </c>
-      <c r="I211">
-        <f t="shared" ref="I211:I213" si="68">(G211/100*MIN(H211,100)/100)</f>
-        <v>0</v>
-      </c>
-      <c r="L211">
-        <f>$AH$19</f>
-        <v>1.6</v>
-      </c>
-      <c r="N211">
-        <f>$AH$47</f>
-        <v>0.64</v>
-      </c>
-      <c r="O211">
-        <f t="shared" si="59"/>
-        <v>0.50740000000000007</v>
-      </c>
-      <c r="Q211">
-        <f>$AH$74</f>
-        <v>43</v>
-      </c>
-      <c r="R211">
-        <f t="shared" si="66"/>
-        <v>0.86186034677094148</v>
-      </c>
-      <c r="S211">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T211">
-        <f t="shared" si="67"/>
-        <v>1</v>
-      </c>
-      <c r="U211">
-        <f t="shared" si="61"/>
-        <v>0.85670984960634056</v>
-      </c>
-      <c r="V211">
-        <v>120</v>
-      </c>
-      <c r="W211">
-        <f t="shared" si="62"/>
-        <v>1.7686145172599206E-2</v>
-      </c>
-      <c r="Y211">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z211">
-        <f t="shared" si="64"/>
-        <v>193.66328963996131</v>
-      </c>
-    </row>
-    <row r="212" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E212" t="s">
-        <v>83</v>
-      </c>
-      <c r="G212">
-        <v>0</v>
-      </c>
-      <c r="H212">
-        <v>0</v>
-      </c>
-      <c r="I212">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="K212" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="L212" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="N212">
-        <f>$AH$48</f>
-        <v>0.72</v>
-      </c>
-      <c r="O212">
-        <f t="shared" si="59"/>
-        <v>0.57100000000000006</v>
-      </c>
-      <c r="Q212">
-        <f>$AH$75</f>
-        <v>45</v>
-      </c>
-      <c r="R212">
-        <f t="shared" si="66"/>
-        <v>1.0181162441707754</v>
-      </c>
-      <c r="S212">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T212">
-        <f t="shared" si="67"/>
-        <v>1</v>
-      </c>
-      <c r="U212">
-        <f t="shared" si="61"/>
-        <v>1.0120319581858332</v>
-      </c>
-      <c r="V212">
-        <v>110</v>
-      </c>
-      <c r="W212">
-        <f t="shared" si="62"/>
-        <v>2.0606200813893666E-2</v>
-      </c>
-      <c r="Y212">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z212">
-        <f t="shared" si="64"/>
-        <v>206.83474066945769</v>
-      </c>
-    </row>
-    <row r="213" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A213">
-        <v>4</v>
-      </c>
-      <c r="D213" t="s">
-        <v>75</v>
-      </c>
-      <c r="E213" t="s">
-        <v>80</v>
-      </c>
-      <c r="G213">
-        <v>95</v>
-      </c>
-      <c r="H213">
-        <v>88</v>
-      </c>
-      <c r="I213">
-        <f t="shared" si="68"/>
-        <v>0.83599999999999997</v>
-      </c>
-      <c r="J213">
-        <f>$AF$3</f>
-        <v>1.3</v>
-      </c>
-      <c r="L213">
-        <f>$AI$17</f>
-        <v>2.9</v>
-      </c>
-      <c r="N213">
-        <f>$AI$45</f>
-        <v>0.75</v>
-      </c>
-      <c r="O213">
-        <f t="shared" si="59"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q213">
-        <f>$AI$72</f>
-        <v>54</v>
-      </c>
-      <c r="R213">
-        <f t="shared" si="66"/>
-        <v>1.2720847291262878</v>
-      </c>
-      <c r="S213">
-        <f t="shared" si="60"/>
-        <v>0.9999999504359468</v>
-      </c>
-      <c r="T213">
-        <f t="shared" si="67"/>
-        <v>1.2507999999999999</v>
-      </c>
-      <c r="U213">
-        <f t="shared" si="61"/>
-        <v>1.5911235003286268</v>
-      </c>
-      <c r="V213">
-        <v>80</v>
-      </c>
-      <c r="W213">
-        <f t="shared" si="62"/>
-        <v>3.1493121806178186E-2</v>
-      </c>
-      <c r="Y213">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z213">
-        <f t="shared" si="64"/>
-        <v>229.89978918510076</v>
-      </c>
-    </row>
-    <row r="214" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E214" t="s">
-        <v>81</v>
-      </c>
-      <c r="G214">
-        <v>0</v>
-      </c>
-      <c r="H214">
-        <v>0</v>
-      </c>
-      <c r="I214">
-        <v>0</v>
-      </c>
-      <c r="L214">
-        <f>$AI$18</f>
-        <v>2.5</v>
-      </c>
-      <c r="N214">
-        <f>$AI$46</f>
-        <v>0.61</v>
-      </c>
-      <c r="O214">
-        <f t="shared" si="59"/>
-        <v>0.48354999999999998</v>
-      </c>
-      <c r="Q214">
-        <f>$AI$73</f>
-        <v>49</v>
-      </c>
-      <c r="R214">
-        <f t="shared" si="66"/>
-        <v>0.93843421889903578</v>
-      </c>
-      <c r="S214">
-        <f t="shared" si="60"/>
-        <v>0.99999627334682795</v>
-      </c>
-      <c r="T214">
-        <f t="shared" si="67"/>
-        <v>1</v>
-      </c>
-      <c r="U214">
-        <f t="shared" si="61"/>
-        <v>0.93843072168017716</v>
-      </c>
-      <c r="V214">
-        <v>90</v>
-      </c>
-      <c r="W214">
-        <f t="shared" si="62"/>
-        <v>1.9222497567587333E-2</v>
-      </c>
-      <c r="Y214">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z214">
-        <f t="shared" si="64"/>
-        <v>157.86476127381098</v>
-      </c>
-    </row>
-    <row r="215" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E215" t="s">
-        <v>82</v>
-      </c>
-      <c r="G215">
-        <v>0</v>
-      </c>
-      <c r="H215">
-        <v>0</v>
-      </c>
-      <c r="I215">
-        <v>0</v>
-      </c>
-      <c r="L215">
-        <f>$AI$19</f>
-        <v>1.6</v>
-      </c>
-      <c r="N215">
-        <f>$AI$47</f>
-        <v>0.64</v>
-      </c>
-      <c r="O215">
-        <f t="shared" si="59"/>
-        <v>0.50740000000000007</v>
-      </c>
-      <c r="Q215">
-        <f>$AI$74</f>
-        <v>50</v>
-      </c>
-      <c r="R215">
-        <f t="shared" si="66"/>
-        <v>1.0054871153505722</v>
-      </c>
-      <c r="S215">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T215">
-        <f t="shared" si="67"/>
-        <v>1</v>
-      </c>
-      <c r="U215">
-        <f t="shared" si="61"/>
-        <v>0.99947830132860371</v>
-      </c>
-      <c r="V215">
-        <v>80</v>
-      </c>
-      <c r="W215">
-        <f t="shared" si="62"/>
-        <v>2.0370192064977751E-2</v>
-      </c>
-      <c r="Y215">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z215">
-        <f t="shared" si="64"/>
-        <v>148.70240207433758</v>
-      </c>
-    </row>
-    <row r="216" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E216" t="s">
-        <v>83</v>
-      </c>
-      <c r="G216">
-        <v>0</v>
-      </c>
-      <c r="H216">
-        <v>0</v>
-      </c>
-      <c r="I216">
-        <v>0</v>
-      </c>
-      <c r="K216" s="2">
-        <v>1.9</v>
-      </c>
-      <c r="L216" s="2">
-        <v>1.9</v>
-      </c>
-      <c r="N216">
-        <f>$AI$48</f>
-        <v>0.72</v>
-      </c>
-      <c r="O216">
-        <f t="shared" si="59"/>
-        <v>0.57100000000000006</v>
-      </c>
-      <c r="Q216">
-        <f>$AI$75</f>
-        <v>50</v>
-      </c>
-      <c r="R216">
-        <f t="shared" si="66"/>
-        <v>1.1306948910936463</v>
-      </c>
-      <c r="S216">
-        <f t="shared" si="60"/>
-        <v>0.99926819758111951</v>
-      </c>
-      <c r="T216">
-        <f t="shared" si="67"/>
-        <v>1</v>
-      </c>
-      <c r="U216">
-        <f t="shared" si="61"/>
-        <v>1.1298674458373281</v>
-      </c>
-      <c r="V216">
-        <v>70</v>
-      </c>
-      <c r="W216">
-        <f t="shared" si="62"/>
-        <v>2.2821507981741773E-2</v>
-      </c>
-      <c r="Y216">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z216">
-        <f t="shared" si="64"/>
-        <v>145.77238223337557</v>
-      </c>
-    </row>
-    <row r="217" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A217">
-        <v>5</v>
-      </c>
-      <c r="D217" t="s">
-        <v>76</v>
-      </c>
-      <c r="E217" t="s">
-        <v>80</v>
-      </c>
-      <c r="G217">
-        <v>0</v>
-      </c>
-      <c r="H217">
-        <v>0</v>
-      </c>
-      <c r="I217">
-        <v>0</v>
-      </c>
-      <c r="L217">
-        <f>$AJ$17</f>
-        <v>2.9</v>
-      </c>
-      <c r="N217">
-        <f>$AJ$45</f>
-        <v>0.75</v>
-      </c>
-      <c r="O217">
-        <f t="shared" si="59"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q217">
-        <f>$AJ$72</f>
-        <v>56</v>
-      </c>
-      <c r="R217">
-        <f t="shared" si="66"/>
-        <v>1.3198285488795851</v>
-      </c>
-      <c r="S217">
-        <f t="shared" si="60"/>
-        <v>0.9999999504359468</v>
-      </c>
-      <c r="T217">
-        <v>1</v>
-      </c>
-      <c r="U217">
-        <f t="shared" si="61"/>
-        <v>1.3198284834635328</v>
-      </c>
-      <c r="V217">
-        <v>50</v>
-      </c>
-      <c r="W217">
-        <f t="shared" si="62"/>
-        <v>2.6392775489114419E-2</v>
-      </c>
-      <c r="Y217">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z217">
-        <f t="shared" si="64"/>
-        <v>120.41703816908453</v>
-      </c>
-    </row>
-    <row r="218" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E218" t="s">
-        <v>81</v>
-      </c>
-      <c r="G218">
-        <v>0</v>
-      </c>
-      <c r="H218">
-        <v>0</v>
-      </c>
-      <c r="I218">
-        <v>0</v>
-      </c>
-      <c r="L218">
-        <f>$AJ$18</f>
-        <v>2.5</v>
-      </c>
-      <c r="N218">
-        <f>$AJ$46</f>
-        <v>0.61</v>
-      </c>
-      <c r="O218">
-        <f t="shared" si="59"/>
-        <v>0.48354999999999998</v>
-      </c>
-      <c r="Q218">
-        <f>$AJ$73</f>
-        <v>51</v>
-      </c>
-      <c r="R218">
-        <f t="shared" si="66"/>
-        <v>0.97873546256970145</v>
-      </c>
-      <c r="S218">
-        <f t="shared" si="60"/>
-        <v>0.99999627334682795</v>
-      </c>
-      <c r="T218">
-        <v>1</v>
-      </c>
-      <c r="U218">
-        <f t="shared" si="61"/>
-        <v>0.97873181516208529</v>
-      </c>
-      <c r="V218">
-        <v>55</v>
-      </c>
-      <c r="W218">
-        <f t="shared" si="62"/>
-        <v>1.9980158125047207E-2</v>
-      </c>
-      <c r="Y218">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z218">
-        <f t="shared" si="64"/>
-        <v>100.27541859008066</v>
-      </c>
-    </row>
-    <row r="219" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E219" t="s">
-        <v>82</v>
-      </c>
-      <c r="G219">
-        <v>0</v>
-      </c>
-      <c r="H219">
-        <v>0</v>
-      </c>
-      <c r="I219">
-        <v>0</v>
-      </c>
-      <c r="L219">
-        <f>$AJ$19</f>
-        <v>1.6</v>
-      </c>
-      <c r="N219">
-        <f>$AJ$47</f>
-        <v>0.64</v>
-      </c>
-      <c r="O219">
-        <f t="shared" si="59"/>
-        <v>0.50740000000000007</v>
-      </c>
-      <c r="Q219">
-        <f>$AJ$74</f>
-        <v>50</v>
-      </c>
-      <c r="R219">
-        <f t="shared" si="66"/>
-        <v>1.0054871153505722</v>
-      </c>
-      <c r="S219">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T219">
-        <v>1</v>
-      </c>
-      <c r="U219">
-        <f t="shared" si="61"/>
-        <v>0.99947830132860371</v>
-      </c>
-      <c r="V219">
-        <v>45</v>
-      </c>
-      <c r="W219">
-        <f t="shared" si="62"/>
-        <v>2.0370192064977751E-2</v>
-      </c>
-      <c r="Y219">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z219">
-        <f t="shared" si="64"/>
-        <v>83.645101166814896</v>
-      </c>
-    </row>
-    <row r="220" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E220" t="s">
-        <v>83</v>
-      </c>
-      <c r="G220">
-        <v>0</v>
-      </c>
-      <c r="H220">
-        <v>0</v>
-      </c>
-      <c r="I220">
-        <v>0</v>
-      </c>
-      <c r="K220" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="L220" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="N220">
-        <f>$AJ$48</f>
-        <v>0.72</v>
-      </c>
-      <c r="O220">
-        <f t="shared" si="59"/>
-        <v>0.57100000000000006</v>
-      </c>
-      <c r="Q220">
-        <f>$AJ$75</f>
-        <v>51</v>
-      </c>
-      <c r="R220">
-        <f t="shared" si="66"/>
-        <v>1.1534721617679149</v>
-      </c>
-      <c r="S220">
-        <f t="shared" si="60"/>
-        <v>0.99846618932067555</v>
-      </c>
-      <c r="T220">
-        <v>1</v>
-      </c>
-      <c r="U220">
-        <f t="shared" si="61"/>
-        <v>1.1517029538478918</v>
-      </c>
-      <c r="V220">
-        <v>40</v>
-      </c>
-      <c r="W220">
-        <f t="shared" si="62"/>
-        <v>2.3232015532340368E-2</v>
-      </c>
-      <c r="Y220">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z220">
-        <f t="shared" si="64"/>
-        <v>84.796856693042344</v>
-      </c>
-    </row>
-    <row r="221" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A221">
-        <v>6</v>
-      </c>
-      <c r="D221" t="s">
-        <v>77</v>
-      </c>
-      <c r="E221" t="s">
-        <v>80</v>
-      </c>
-      <c r="G221">
-        <v>0</v>
-      </c>
-      <c r="H221">
-        <v>0</v>
-      </c>
-      <c r="I221">
-        <v>0</v>
-      </c>
-      <c r="L221">
-        <f>$AK$17</f>
-        <v>2.9</v>
-      </c>
-      <c r="N221">
-        <f>$AK$45</f>
-        <v>0.75</v>
-      </c>
-      <c r="O221">
-        <f t="shared" si="59"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q221">
-        <f>$AK$72</f>
-        <v>20</v>
-      </c>
-      <c r="R221">
-        <f t="shared" si="66"/>
-        <v>0.5052226861752882</v>
-      </c>
-      <c r="S221">
-        <f t="shared" si="60"/>
-        <v>0.9999999504359468</v>
-      </c>
-      <c r="T221">
-        <v>1</v>
-      </c>
-      <c r="U221">
-        <f t="shared" si="61"/>
-        <v>0.50522266113440406</v>
-      </c>
-      <c r="V221">
-        <v>30</v>
-      </c>
-      <c r="W221">
-        <f t="shared" si="62"/>
-        <v>1.1078186029326796E-2</v>
-      </c>
-      <c r="Y221">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z221">
-        <f t="shared" si="64"/>
-        <v>30.326534255282102</v>
-      </c>
-    </row>
-    <row r="222" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E222" t="s">
-        <v>81</v>
-      </c>
-      <c r="G222">
-        <v>0</v>
-      </c>
-      <c r="H222">
-        <v>0</v>
-      </c>
-      <c r="I222">
-        <v>0</v>
-      </c>
-      <c r="L222">
-        <f>$AK$18</f>
-        <v>2.5</v>
-      </c>
-      <c r="N222">
-        <f>$AK$46</f>
-        <v>0.61</v>
-      </c>
-      <c r="O222">
-        <f t="shared" si="59"/>
-        <v>0.48354999999999998</v>
-      </c>
-      <c r="Q222">
-        <f>$AK$73</f>
-        <v>27</v>
-      </c>
-      <c r="R222">
-        <f t="shared" si="66"/>
-        <v>0.52017847077168489</v>
-      </c>
-      <c r="S222">
-        <f t="shared" si="60"/>
-        <v>0.99999627334682795</v>
-      </c>
-      <c r="T222">
-        <v>1</v>
-      </c>
-      <c r="U222">
-        <f t="shared" si="61"/>
-        <v>0.52017653224693672</v>
-      </c>
-      <c r="V222">
-        <v>90</v>
-      </c>
-      <c r="W222">
-        <f t="shared" si="62"/>
-        <v>1.135931880624241E-2</v>
-      </c>
-      <c r="Y222">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z222">
-        <f t="shared" si="64"/>
-        <v>93.288405696265798</v>
-      </c>
-    </row>
-    <row r="223" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E223" t="s">
-        <v>82</v>
-      </c>
-      <c r="G223">
-        <v>0</v>
-      </c>
-      <c r="H223">
-        <v>0</v>
-      </c>
-      <c r="I223">
-        <v>0</v>
-      </c>
-      <c r="L223">
-        <f>$AK$19</f>
-        <v>1.6</v>
-      </c>
-      <c r="N223">
-        <f>$AK$47</f>
-        <v>0.64</v>
-      </c>
-      <c r="O223">
-        <f t="shared" si="59"/>
-        <v>0.50740000000000007</v>
-      </c>
-      <c r="Q223">
-        <f>$AK$74</f>
-        <v>32</v>
-      </c>
-      <c r="R223">
-        <f t="shared" si="66"/>
-        <v>0.64511931548462409</v>
-      </c>
-      <c r="S223">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T223">
-        <v>1</v>
-      </c>
-      <c r="U223">
-        <f t="shared" si="61"/>
-        <v>0.64126406768527744</v>
-      </c>
-      <c r="V223">
-        <v>80</v>
-      </c>
-      <c r="W223">
-        <f t="shared" si="62"/>
-        <v>1.3635764472483216E-2</v>
-      </c>
-      <c r="Y223">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z223">
-        <f t="shared" si="64"/>
-        <v>99.54108064912748</v>
-      </c>
-    </row>
-    <row r="224" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E224" t="s">
-        <v>83</v>
-      </c>
-      <c r="G224">
-        <v>0</v>
-      </c>
-      <c r="H224">
-        <v>0</v>
-      </c>
-      <c r="I224">
-        <v>0</v>
-      </c>
-      <c r="K224" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="L224" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="N224">
-        <f>$AK$48</f>
-        <v>0.72</v>
-      </c>
-      <c r="O224">
-        <f t="shared" si="59"/>
-        <v>0.57100000000000006</v>
-      </c>
-      <c r="Q224">
-        <f>$AK$75</f>
-        <v>34</v>
-      </c>
-      <c r="R224">
-        <f t="shared" si="66"/>
-        <v>0.77753323213623582</v>
-      </c>
-      <c r="S224">
-        <f t="shared" si="60"/>
-        <v>0.99402397710499402</v>
-      </c>
-      <c r="T224">
-        <v>1</v>
-      </c>
-      <c r="U224">
-        <f t="shared" si="61"/>
-        <v>0.77288667573936165</v>
-      </c>
-      <c r="V224">
-        <v>70</v>
-      </c>
-      <c r="W224">
-        <f t="shared" si="62"/>
-        <v>1.6110269503900002E-2</v>
-      </c>
-      <c r="Y224">
-        <f t="shared" si="63"/>
-        <v>91.25</v>
-      </c>
-      <c r="Z224">
-        <f t="shared" si="64"/>
-        <v>102.90434645616126</v>
-      </c>
-    </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A231" t="s">
-        <v>99</v>
-      </c>
-      <c r="B231" t="s">
-        <v>98</v>
-      </c>
-      <c r="C231" t="s">
-        <v>98</v>
-      </c>
-      <c r="D231" t="s">
-        <v>72</v>
-      </c>
-      <c r="E231" t="s">
-        <v>80</v>
-      </c>
-      <c r="G231">
-        <v>0</v>
-      </c>
-      <c r="H231">
-        <v>0</v>
-      </c>
-      <c r="I231">
-        <v>0</v>
-      </c>
-      <c r="L231">
-        <f>$AF$21</f>
-        <v>1.5</v>
-      </c>
-      <c r="M231" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="N231" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="O231">
-        <f>(0.795 * N231) - 0.0014</f>
-        <v>0.39610000000000001</v>
-      </c>
-      <c r="Q231">
-        <f>$AF$76</f>
-        <v>58</v>
-      </c>
       <c r="R231">
         <f>(104.7 * O231 + 0.307 * Q231- 15) * POWER(Q231, 0.75) * 10^-3</f>
-        <v>0.93058437094840885</v>
+        <v>1.7917898456122741</v>
       </c>
       <c r="S231">
         <f>1-EXP(-2*POWER(L231,2))</f>
-        <v>0.98889100346175773</v>
+        <v>0.9999999504359468</v>
       </c>
       <c r="T231">
         <v>1</v>
       </c>
       <c r="U231">
         <f>R231 * S231 * T231</f>
-        <v>0.92024651239300059</v>
+        <v>1.7917897568039067</v>
       </c>
       <c r="V231">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="W231">
         <f>(U231 * 0.0188) + 0.00158</f>
-        <v>1.8880634432988413E-2</v>
+        <v>3.5265647427913445E-2</v>
       </c>
       <c r="Y231">
         <f>$AF$4</f>
@@ -13405,11 +13404,11 @@
       </c>
       <c r="Z231">
         <f>V231*W231*Y231</f>
-        <v>43.071447300254817</v>
+        <v>160.89951638985508</v>
       </c>
       <c r="AA231">
         <f>SUM(Z231:Z254)*10^-3</f>
-        <v>1.3279574495523139</v>
+        <v>3.7710363373989564</v>
       </c>
     </row>
     <row r="232" spans="1:27" x14ac:dyDescent="0.2">
@@ -13426,44 +13425,42 @@
         <v>0</v>
       </c>
       <c r="L232">
-        <f>$AF$22</f>
-        <v>2</v>
-      </c>
-      <c r="M232" s="2">
-        <v>0.51</v>
-      </c>
-      <c r="N232" s="2">
-        <v>0.51</v>
+        <f>$AF$18</f>
+        <v>2.5</v>
+      </c>
+      <c r="N232">
+        <f>$AF$46</f>
+        <v>0.61</v>
       </c>
       <c r="O232">
         <f t="shared" ref="O232:O254" si="69">(0.795 * N232) - 0.0014</f>
-        <v>0.40405000000000002</v>
+        <v>0.48354999999999998</v>
       </c>
       <c r="Q232">
-        <f>$AF$77</f>
-        <v>61</v>
+        <f>$AF$73</f>
+        <v>75</v>
       </c>
       <c r="R232">
         <f>(104.7 * O232 + 0.307 * Q232- 15) * POWER(Q232, 0.75) * 10^-3</f>
-        <v>1.0047270997102939</v>
+        <v>1.4948026034112167</v>
       </c>
       <c r="S232">
         <f t="shared" ref="S232:S254" si="70">1-EXP(-2*POWER(L232,2))</f>
-        <v>0.99966453737209748</v>
+        <v>0.99999627334682795</v>
       </c>
       <c r="T232">
         <v>1</v>
       </c>
       <c r="U232">
         <f t="shared" ref="U232:U254" si="71">R232 * S232 * T232</f>
-        <v>1.0043900513171002</v>
+        <v>1.494797032800353</v>
       </c>
       <c r="V232">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="W232">
         <f t="shared" ref="W232:W254" si="72">(U232 * 0.0188) + 0.00158</f>
-        <v>2.0462532964761488E-2</v>
+        <v>2.9682184216646638E-2</v>
       </c>
       <c r="Y232">
         <f t="shared" ref="Y232:Y254" si="73">$AF$4</f>
@@ -13471,7 +13468,7 @@
       </c>
       <c r="Z232">
         <f t="shared" ref="Z232:Z254" si="74">V232*W232*Y232</f>
-        <v>37.344122660689713</v>
+        <v>108.33997239076024</v>
       </c>
     </row>
     <row r="233" spans="1:27" x14ac:dyDescent="0.2">
@@ -13488,44 +13485,42 @@
         <v>0</v>
       </c>
       <c r="L233">
-        <f>$AF$23</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M233" s="2">
-        <v>0.52</v>
-      </c>
-      <c r="N233" s="2">
-        <v>0.52</v>
+        <f>$AF$19</f>
+        <v>1.6</v>
+      </c>
+      <c r="N233">
+        <f>$AF$47</f>
+        <v>0.64</v>
       </c>
       <c r="O233">
         <f t="shared" si="69"/>
-        <v>0.41200000000000003</v>
+        <v>0.50740000000000007</v>
       </c>
       <c r="Q233">
-        <f>$AF$78</f>
-        <v>63</v>
+        <f>$AF$74</f>
+        <v>69</v>
       </c>
       <c r="R233">
         <f t="shared" ref="R233:R238" si="75">(104.7 * O233 + 0.307 * Q233- 15) * POWER(Q233, 0.75) * 10^-3</f>
-        <v>1.0616768308982532</v>
+        <v>1.4198696820048529</v>
       </c>
       <c r="S233">
         <f t="shared" si="70"/>
-        <v>0.99993747849622516</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T233">
         <v>1</v>
       </c>
       <c r="U233">
         <f t="shared" si="71"/>
-        <v>1.0616104532662625</v>
+        <v>1.4113845082772669</v>
       </c>
       <c r="V233">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="W233">
         <f t="shared" si="72"/>
-        <v>2.1538276521405737E-2</v>
+        <v>2.811402875561262E-2</v>
       </c>
       <c r="Y233">
         <f t="shared" si="73"/>
@@ -13533,7 +13528,7 @@
       </c>
       <c r="Z233">
         <f t="shared" si="74"/>
-        <v>37.341986918987196</v>
+        <v>97.485394710086752</v>
       </c>
     </row>
     <row r="234" spans="1:27" x14ac:dyDescent="0.2">
@@ -13549,45 +13544,45 @@
       <c r="I234">
         <v>0</v>
       </c>
-      <c r="L234">
-        <f>$AF$24</f>
-        <v>1.7</v>
-      </c>
-      <c r="M234" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="N234" s="2">
-        <v>0.53</v>
+      <c r="K234" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="L234" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="N234">
+        <f>$AF$48</f>
+        <v>0.72</v>
       </c>
       <c r="O234">
         <f t="shared" si="69"/>
-        <v>0.41995000000000005</v>
+        <v>0.57100000000000006</v>
       </c>
       <c r="Q234">
-        <f>$AF$79</f>
-        <v>60</v>
+        <f>$AF$75</f>
+        <v>69</v>
       </c>
       <c r="R234">
         <f t="shared" si="75"/>
-        <v>1.0216186875211368</v>
+        <v>1.5792888783210146</v>
       </c>
       <c r="S234">
         <f t="shared" si="70"/>
-        <v>0.99691128459176326</v>
+        <v>0.99926819758111951</v>
       </c>
       <c r="T234">
         <v>1</v>
       </c>
       <c r="U234">
         <f t="shared" si="71"/>
-        <v>1.0184631981396477</v>
+        <v>1.5781331508997483</v>
       </c>
       <c r="V234">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="W234">
         <f t="shared" si="72"/>
-        <v>2.072710812502538E-2</v>
+        <v>3.124890323691527E-2</v>
       </c>
       <c r="Y234">
         <f t="shared" si="73"/>
@@ -13595,7 +13590,7 @@
       </c>
       <c r="Z234">
         <f t="shared" si="74"/>
-        <v>47.28371541021415</v>
+        <v>142.57312101842592</v>
       </c>
     </row>
     <row r="235" spans="1:27" x14ac:dyDescent="0.2">
@@ -13618,44 +13613,42 @@
         <v>0</v>
       </c>
       <c r="L235">
-        <f>$AG$21</f>
-        <v>1.5</v>
-      </c>
-      <c r="M235" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="N235" s="2">
-        <v>0.5</v>
+        <f>$AG$17</f>
+        <v>2.9</v>
+      </c>
+      <c r="N235">
+        <f>$AG$45</f>
+        <v>0.75</v>
       </c>
       <c r="O235">
         <f t="shared" si="69"/>
-        <v>0.39610000000000001</v>
+        <v>0.5948500000000001</v>
       </c>
       <c r="Q235">
-        <f>$AG$76</f>
-        <v>50</v>
+        <f>$AG$72</f>
+        <v>62</v>
       </c>
       <c r="R235">
         <f t="shared" si="75"/>
-        <v>0.78637350780019211</v>
+        <v>1.4652245899459331</v>
       </c>
       <c r="S235">
         <f t="shared" si="70"/>
-        <v>0.98889100346175773</v>
+        <v>0.9999999504359468</v>
       </c>
       <c r="T235">
         <v>1</v>
       </c>
       <c r="U235">
         <f t="shared" si="71"/>
-        <v>0.7776376872242744</v>
+        <v>1.4652245173234635</v>
       </c>
       <c r="V235">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="W235">
         <f t="shared" si="72"/>
-        <v>1.6199588519816361E-2</v>
+        <v>2.9126220925681116E-2</v>
       </c>
       <c r="Y235">
         <f t="shared" si="73"/>
@@ -13663,7 +13656,7 @@
       </c>
       <c r="Z235">
         <f t="shared" si="74"/>
-        <v>73.910622621662142</v>
+        <v>265.77676594684021</v>
       </c>
     </row>
     <row r="236" spans="1:27" x14ac:dyDescent="0.2">
@@ -13680,44 +13673,42 @@
         <v>0</v>
       </c>
       <c r="L236">
-        <f>$AG$22</f>
-        <v>2</v>
-      </c>
-      <c r="M236" s="2">
-        <v>0.51</v>
-      </c>
-      <c r="N236" s="2">
-        <v>0.51</v>
+        <f>$AG$18</f>
+        <v>2.5</v>
+      </c>
+      <c r="N236">
+        <f>$AG$46</f>
+        <v>0.61</v>
       </c>
       <c r="O236">
         <f t="shared" si="69"/>
-        <v>0.40405000000000002</v>
+        <v>0.48354999999999998</v>
       </c>
       <c r="Q236">
-        <f>$AG$77</f>
+        <f>$AG$73</f>
         <v>55</v>
       </c>
       <c r="R236">
         <f t="shared" si="75"/>
-        <v>0.89245542667763567</v>
+        <v>1.0605624381175847</v>
       </c>
       <c r="S236">
         <f t="shared" si="70"/>
-        <v>0.99966453737209748</v>
+        <v>0.99999627334682795</v>
       </c>
       <c r="T236">
         <v>1</v>
       </c>
       <c r="U236">
         <f t="shared" si="71"/>
-        <v>0.89215604123491654</v>
+        <v>1.0605584857692105</v>
       </c>
       <c r="V236">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="W236">
         <f t="shared" si="72"/>
-        <v>1.8352533575216434E-2</v>
+        <v>2.1518499532461158E-2</v>
       </c>
       <c r="Y236">
         <f t="shared" si="73"/>
@@ -13725,7 +13716,7 @@
       </c>
       <c r="Z236">
         <f t="shared" si="74"/>
-        <v>100.48012132430998</v>
+        <v>235.6275698804497</v>
       </c>
     </row>
     <row r="237" spans="1:27" x14ac:dyDescent="0.2">
@@ -13742,44 +13733,42 @@
         <v>0</v>
       </c>
       <c r="L237">
-        <f>$AG$23</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M237" s="2">
-        <v>0.52</v>
-      </c>
-      <c r="N237" s="2">
-        <v>0.52</v>
+        <f>$AG$19</f>
+        <v>1.6</v>
+      </c>
+      <c r="N237">
+        <f>$AG$47</f>
+        <v>0.64</v>
       </c>
       <c r="O237">
         <f t="shared" si="69"/>
-        <v>0.41200000000000003</v>
+        <v>0.50740000000000007</v>
       </c>
       <c r="Q237">
-        <f>$AG$78</f>
+        <f>$AG$74</f>
         <v>55</v>
       </c>
       <c r="R237">
         <f t="shared" si="75"/>
-        <v>0.90926612782163052</v>
+        <v>1.1109945415495692</v>
       </c>
       <c r="S237">
         <f t="shared" si="70"/>
-        <v>0.99993747849622516</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T237">
         <v>1</v>
       </c>
       <c r="U237">
         <f t="shared" si="71"/>
-        <v>0.90920927913598759</v>
+        <v>1.1043552127330423</v>
       </c>
       <c r="V237">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="W237">
         <f t="shared" si="72"/>
-        <v>1.8673134447756569E-2</v>
+        <v>2.2341877999381195E-2</v>
       </c>
       <c r="Y237">
         <f t="shared" si="73"/>
@@ -13787,7 +13776,7 @@
       </c>
       <c r="Z237">
         <f t="shared" si="74"/>
-        <v>93.715793509678278</v>
+        <v>234.4500822560064</v>
       </c>
     </row>
     <row r="238" spans="1:27" x14ac:dyDescent="0.2">
@@ -13803,45 +13792,45 @@
       <c r="I238">
         <v>0</v>
       </c>
-      <c r="L238">
-        <f>$AG$24</f>
-        <v>1.7</v>
-      </c>
-      <c r="M238" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="N238" s="2">
-        <v>0.53</v>
+      <c r="K238" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="L238" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="N238">
+        <f>$AG$48</f>
+        <v>0.72</v>
       </c>
       <c r="O238">
         <f t="shared" si="69"/>
-        <v>0.41995000000000005</v>
+        <v>0.57100000000000006</v>
       </c>
       <c r="Q238">
-        <f>$AG$79</f>
-        <v>50</v>
+        <f>$AG$75</f>
+        <v>55</v>
       </c>
       <c r="R238">
         <f t="shared" si="75"/>
-        <v>0.83332642370384502</v>
+        <v>1.2454801507015281</v>
       </c>
       <c r="S238">
         <f t="shared" si="70"/>
-        <v>0.99691128459176326</v>
+        <v>0.99846618932067555</v>
       </c>
       <c r="T238">
         <v>1</v>
       </c>
       <c r="U238">
         <f t="shared" si="71"/>
-        <v>0.83075251553886009</v>
+        <v>1.2435698199454954</v>
       </c>
       <c r="V238">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="W238">
         <f t="shared" si="72"/>
-        <v>1.719814729213057E-2</v>
+        <v>2.4959112614975316E-2</v>
       </c>
       <c r="Y238">
         <f t="shared" si="73"/>
@@ -13849,7 +13838,7 @@
       </c>
       <c r="Z238">
         <f t="shared" si="74"/>
-        <v>86.313201722380299</v>
+        <v>250.52709287281473</v>
       </c>
     </row>
     <row r="239" spans="1:27" x14ac:dyDescent="0.2">
@@ -13863,59 +13852,57 @@
         <v>80</v>
       </c>
       <c r="G239">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H239">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I239">
         <f>(G239/100*MIN(H239,100)/100)</f>
-        <v>0.80040000000000011</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="J239">
         <f>$AF$3</f>
         <v>1.3</v>
       </c>
       <c r="L239">
-        <f>$AH$21</f>
-        <v>1.5</v>
-      </c>
-      <c r="M239" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="N239" s="2">
-        <v>0.53</v>
+        <f>$AH$17</f>
+        <v>2.9</v>
+      </c>
+      <c r="N239">
+        <f>$AH$45</f>
+        <v>0.75</v>
       </c>
       <c r="O239">
         <f t="shared" si="69"/>
-        <v>0.41995000000000005</v>
+        <v>0.5948500000000001</v>
       </c>
       <c r="Q239">
-        <f>$AH$76</f>
-        <v>35</v>
+        <f>$AH$72</f>
+        <v>44</v>
       </c>
       <c r="R239">
         <f>(104.7 * O239 + 0.307 * Q239- 15) * POWER(Q239, 0.75) * 10^-3</f>
-        <v>0.57146823458155449</v>
+        <v>1.0385156413271623</v>
       </c>
       <c r="S239">
         <f t="shared" si="70"/>
-        <v>0.98889100346175773</v>
+        <v>0.9999999504359468</v>
       </c>
       <c r="T239">
         <f>(I239 * J239) + (1 - I239)</f>
-        <v>1.2401200000000001</v>
+        <v>1.2295</v>
       </c>
       <c r="U239">
         <f t="shared" si="71"/>
-        <v>0.70081636134343506</v>
+        <v>1.2768549177256379</v>
       </c>
       <c r="V239">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="W239">
         <f t="shared" si="72"/>
-        <v>1.475534759325658E-2</v>
+        <v>2.5584872453241994E-2</v>
       </c>
       <c r="Y239">
         <f t="shared" si="73"/>
@@ -13923,7 +13910,7 @@
       </c>
       <c r="Z239">
         <f t="shared" si="74"/>
-        <v>80.785528073079774</v>
+        <v>280.15435336299987</v>
       </c>
     </row>
     <row r="240" spans="1:27" x14ac:dyDescent="0.2">
@@ -13941,30 +13928,28 @@
         <v>0</v>
       </c>
       <c r="L240">
-        <f>$AH$22</f>
-        <v>2</v>
-      </c>
-      <c r="M240" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="N240" s="2">
-        <v>0.53</v>
+        <f>$AH$18</f>
+        <v>2.5</v>
+      </c>
+      <c r="N240">
+        <f>$AH$46</f>
+        <v>0.61</v>
       </c>
       <c r="O240">
         <f t="shared" si="69"/>
-        <v>0.41995000000000005</v>
+        <v>0.48354999999999998</v>
       </c>
       <c r="Q240">
-        <f>$AH$77</f>
-        <v>40</v>
+        <f>$AH$73</f>
+        <v>42</v>
       </c>
       <c r="R240">
         <f t="shared" ref="R240:R254" si="76">(104.7 * O240 + 0.307 * Q240- 15) * POWER(Q240, 0.75) * 10^-3</f>
-        <v>0.65607870804581636</v>
+        <v>0.80052120768394575</v>
       </c>
       <c r="S240">
         <f t="shared" si="70"/>
-        <v>0.99966453737209748</v>
+        <v>0.99999627334682795</v>
       </c>
       <c r="T240">
         <f t="shared" ref="T240:T246" si="77">(I240 * J240) + (1 - I240)</f>
@@ -13972,14 +13957,14 @@
       </c>
       <c r="U240">
         <f t="shared" si="71"/>
-        <v>0.65585861815830437</v>
+        <v>0.80051822441904785</v>
       </c>
       <c r="V240">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="W240">
         <f t="shared" si="72"/>
-        <v>1.3910142021376122E-2</v>
+        <v>1.6629742619078101E-2</v>
       </c>
       <c r="Y240">
         <f t="shared" si="73"/>
@@ -13987,7 +13972,7 @@
       </c>
       <c r="Z240">
         <f t="shared" si="74"/>
-        <v>88.851032161539976</v>
+        <v>197.27032181881395</v>
       </c>
     </row>
     <row r="241" spans="1:26" x14ac:dyDescent="0.2">
@@ -14005,30 +13990,28 @@
         <v>0</v>
       </c>
       <c r="L241">
-        <f>$AH$23</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M241" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="N241" s="2">
-        <v>0.53</v>
+        <f>$AH$19</f>
+        <v>1.6</v>
+      </c>
+      <c r="N241">
+        <f>$AH$47</f>
+        <v>0.64</v>
       </c>
       <c r="O241">
         <f t="shared" si="69"/>
-        <v>0.41995000000000005</v>
+        <v>0.50740000000000007</v>
       </c>
       <c r="Q241">
-        <f>$AH$78</f>
-        <v>40</v>
+        <f>$AH$74</f>
+        <v>43</v>
       </c>
       <c r="R241">
         <f t="shared" si="76"/>
-        <v>0.65607870804581636</v>
+        <v>0.86186034677094148</v>
       </c>
       <c r="S241">
         <f t="shared" si="70"/>
-        <v>0.99993747849622516</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T241">
         <f t="shared" si="77"/>
@@ -14036,14 +14019,14 @@
       </c>
       <c r="U241">
         <f t="shared" si="71"/>
-        <v>0.65603768901839465</v>
+        <v>0.85670984960634056</v>
       </c>
       <c r="V241">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="W241">
         <f t="shared" si="72"/>
-        <v>1.391350855354582E-2</v>
+        <v>1.7686145172599206E-2</v>
       </c>
       <c r="Y241">
         <f t="shared" si="73"/>
@@ -14051,7 +14034,7 @@
       </c>
       <c r="Z241">
         <f t="shared" si="74"/>
-        <v>76.176459330663363</v>
+        <v>193.66328963996131</v>
       </c>
     </row>
     <row r="242" spans="1:26" x14ac:dyDescent="0.2">
@@ -14068,31 +14051,31 @@
         <f t="shared" si="78"/>
         <v>0</v>
       </c>
-      <c r="L242">
-        <f>$AH$24</f>
-        <v>1.7</v>
-      </c>
-      <c r="M242" s="2">
-        <v>0.53</v>
-      </c>
-      <c r="N242" s="2">
-        <v>0.53</v>
+      <c r="K242" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="L242" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="N242">
+        <f>$AH$48</f>
+        <v>0.72</v>
       </c>
       <c r="O242">
         <f t="shared" si="69"/>
-        <v>0.41995000000000005</v>
+        <v>0.57100000000000006</v>
       </c>
       <c r="Q242">
-        <f>$AH$79</f>
-        <v>35</v>
+        <f>$AH$75</f>
+        <v>45</v>
       </c>
       <c r="R242">
         <f t="shared" si="76"/>
-        <v>0.57146823458155449</v>
+        <v>1.0181162441707754</v>
       </c>
       <c r="S242">
         <f t="shared" si="70"/>
-        <v>0.99691128459176326</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T242">
         <f t="shared" si="77"/>
@@ -14100,14 +14083,14 @@
       </c>
       <c r="U242">
         <f t="shared" si="71"/>
-        <v>0.56970313184008459</v>
+        <v>1.0120319581858332</v>
       </c>
       <c r="V242">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="W242">
         <f t="shared" si="72"/>
-        <v>1.2290418878593591E-2</v>
+        <v>2.0606200813893666E-2</v>
       </c>
       <c r="Y242">
         <f t="shared" si="73"/>
@@ -14115,7 +14098,7 @@
       </c>
       <c r="Z242">
         <f t="shared" si="74"/>
-        <v>56.075036133583261</v>
+        <v>206.83474066945769</v>
       </c>
     </row>
     <row r="243" spans="1:26" x14ac:dyDescent="0.2">
@@ -14143,28 +14126,28 @@
         <v>1.3</v>
       </c>
       <c r="L243">
-        <f>$AI$21</f>
-        <v>1.5</v>
+        <f>$AI$17</f>
+        <v>2.9</v>
       </c>
       <c r="N243">
-        <f>$AI$49</f>
-        <v>0.51</v>
+        <f>$AI$45</f>
+        <v>0.75</v>
       </c>
       <c r="O243">
         <f t="shared" si="69"/>
-        <v>0.40405000000000002</v>
+        <v>0.5948500000000001</v>
       </c>
       <c r="Q243">
-        <f>$AI$76</f>
-        <v>40</v>
+        <f>$AI$72</f>
+        <v>54</v>
       </c>
       <c r="R243">
         <f t="shared" si="76"/>
-        <v>0.62960048723980899</v>
+        <v>1.2720847291262878</v>
       </c>
       <c r="S243">
         <f t="shared" si="70"/>
-        <v>0.98889100346175773</v>
+        <v>0.9999999504359468</v>
       </c>
       <c r="T243">
         <f t="shared" si="77"/>
@@ -14172,14 +14155,14 @@
       </c>
       <c r="U243">
         <f t="shared" si="71"/>
-        <v>0.77875590701431807</v>
+        <v>1.5911235003286268</v>
       </c>
       <c r="V243">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="W243">
         <f t="shared" si="72"/>
-        <v>1.6220611051869182E-2</v>
+        <v>3.1493121806178186E-2</v>
       </c>
       <c r="Y243">
         <f t="shared" si="73"/>
@@ -14187,7 +14170,7 @@
       </c>
       <c r="Z243">
         <f t="shared" si="74"/>
-        <v>59.205230339322519</v>
+        <v>229.89978918510076</v>
       </c>
     </row>
     <row r="244" spans="1:26" x14ac:dyDescent="0.2">
@@ -14204,28 +14187,28 @@
         <v>0</v>
       </c>
       <c r="L244">
-        <f>$AI$22</f>
-        <v>2</v>
+        <f>$AI$18</f>
+        <v>2.5</v>
       </c>
       <c r="N244">
-        <f>$AI$50</f>
-        <v>0.55000000000000004</v>
+        <f>$AI$46</f>
+        <v>0.61</v>
       </c>
       <c r="O244">
         <f t="shared" si="69"/>
-        <v>0.43585000000000007</v>
+        <v>0.48354999999999998</v>
       </c>
       <c r="Q244">
-        <f>$AI$77</f>
-        <v>45</v>
+        <f>$AI$73</f>
+        <v>49</v>
       </c>
       <c r="R244">
         <f t="shared" si="76"/>
-        <v>0.77226516609487061</v>
+        <v>0.93843421889903578</v>
       </c>
       <c r="S244">
         <f t="shared" si="70"/>
-        <v>0.99966453737209748</v>
+        <v>0.99999627334682795</v>
       </c>
       <c r="T244">
         <f t="shared" si="77"/>
@@ -14233,14 +14216,14 @@
       </c>
       <c r="U244">
         <f t="shared" si="71"/>
-        <v>0.77200609999281489</v>
+        <v>0.93843072168017716</v>
       </c>
       <c r="V244">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="W244">
         <f t="shared" si="72"/>
-        <v>1.609371467986492E-2</v>
+        <v>1.9222497567587333E-2</v>
       </c>
       <c r="Y244">
         <f t="shared" si="73"/>
@@ -14248,7 +14231,7 @@
       </c>
       <c r="Z244">
         <f t="shared" si="74"/>
-        <v>66.084815904195324</v>
+        <v>157.86476127381098</v>
       </c>
     </row>
     <row r="245" spans="1:26" x14ac:dyDescent="0.2">
@@ -14265,28 +14248,28 @@
         <v>0</v>
       </c>
       <c r="L245">
-        <f>$AI$23</f>
-        <v>2.2000000000000002</v>
+        <f>$AI$19</f>
+        <v>1.6</v>
       </c>
       <c r="N245">
-        <f>$AI$51</f>
-        <v>0.59</v>
+        <f>$AI$47</f>
+        <v>0.64</v>
       </c>
       <c r="O245">
         <f t="shared" si="69"/>
-        <v>0.46765000000000001</v>
+        <v>0.50740000000000007</v>
       </c>
       <c r="Q245">
-        <f>$AI$78</f>
-        <v>45</v>
+        <f>$AI$74</f>
+        <v>50</v>
       </c>
       <c r="R245">
         <f t="shared" si="76"/>
-        <v>0.8301124785833186</v>
+        <v>1.0054871153505722</v>
       </c>
       <c r="S245">
         <f t="shared" si="70"/>
-        <v>0.99993747849622516</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T245">
         <f t="shared" si="77"/>
@@ -14294,14 +14277,14 @@
       </c>
       <c r="U245">
         <f t="shared" si="71"/>
-        <v>0.83006057870285532</v>
+        <v>0.99947830132860371</v>
       </c>
       <c r="V245">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="W245">
         <f t="shared" si="72"/>
-        <v>1.7185138879613683E-2</v>
+        <v>2.0370192064977751E-2</v>
       </c>
       <c r="Y245">
         <f t="shared" si="73"/>
@@ -14309,7 +14292,7 @@
       </c>
       <c r="Z245">
         <f t="shared" si="74"/>
-        <v>62.725756910589936</v>
+        <v>148.70240207433758</v>
       </c>
     </row>
     <row r="246" spans="1:26" x14ac:dyDescent="0.2">
@@ -14325,29 +14308,31 @@
       <c r="I246">
         <v>0</v>
       </c>
-      <c r="L246">
-        <f>$AI$24</f>
-        <v>1.7</v>
+      <c r="K246" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="L246" s="2">
+        <v>1.9</v>
       </c>
       <c r="N246">
-        <f>$AI$52</f>
-        <v>0.57999999999999996</v>
+        <f>$AI$48</f>
+        <v>0.72</v>
       </c>
       <c r="O246">
         <f t="shared" si="69"/>
-        <v>0.4597</v>
+        <v>0.57100000000000006</v>
       </c>
       <c r="Q246">
-        <f>$AI$79</f>
-        <v>42</v>
+        <f>$AI$75</f>
+        <v>50</v>
       </c>
       <c r="R246">
         <f t="shared" si="76"/>
-        <v>0.7593235966549482</v>
+        <v>1.1306948910936463</v>
       </c>
       <c r="S246">
         <f t="shared" si="70"/>
-        <v>0.99691128459176326</v>
+        <v>0.99926819758111951</v>
       </c>
       <c r="T246">
         <f t="shared" si="77"/>
@@ -14355,14 +14340,14 @@
       </c>
       <c r="U246">
         <f t="shared" si="71"/>
-        <v>0.75697826216212227</v>
+        <v>1.1298674458373281</v>
       </c>
       <c r="V246">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="W246">
         <f t="shared" si="72"/>
-        <v>1.5811191328647899E-2</v>
+        <v>2.2821507981741773E-2</v>
       </c>
       <c r="Y246">
         <f t="shared" si="73"/>
@@ -14370,7 +14355,7 @@
       </c>
       <c r="Z246">
         <f t="shared" si="74"/>
-        <v>50.496992305869227</v>
+        <v>145.77238223337557</v>
       </c>
     </row>
     <row r="247" spans="1:26" x14ac:dyDescent="0.2">
@@ -14393,42 +14378,42 @@
         <v>0</v>
       </c>
       <c r="L247">
-        <f>$AJ$21</f>
-        <v>1.5</v>
+        <f>$AJ$17</f>
+        <v>2.9</v>
       </c>
       <c r="N247">
-        <f>$AJ$49</f>
-        <v>0.51</v>
+        <f>$AJ$45</f>
+        <v>0.75</v>
       </c>
       <c r="O247">
         <f t="shared" si="69"/>
-        <v>0.40405000000000002</v>
+        <v>0.5948500000000001</v>
       </c>
       <c r="Q247">
-        <f>$AJ$76</f>
-        <v>45</v>
+        <f>$AJ$72</f>
+        <v>56</v>
       </c>
       <c r="R247">
         <f t="shared" si="76"/>
-        <v>0.71441785360642229</v>
+        <v>1.3198285488795851</v>
       </c>
       <c r="S247">
         <f t="shared" si="70"/>
-        <v>0.98889100346175773</v>
+        <v>0.9999999504359468</v>
       </c>
       <c r="T247">
         <v>1</v>
       </c>
       <c r="U247">
         <f t="shared" si="71"/>
-        <v>0.70648138814385009</v>
+        <v>1.3198284834635328</v>
       </c>
       <c r="V247">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="W247">
         <f t="shared" si="72"/>
-        <v>1.4861850097104381E-2</v>
+        <v>2.6392775489114419E-2</v>
       </c>
       <c r="Y247">
         <f t="shared" si="73"/>
@@ -14436,7 +14421,7 @@
       </c>
       <c r="Z247">
         <f t="shared" si="74"/>
-        <v>33.903595534019367</v>
+        <v>120.41703816908453</v>
       </c>
     </row>
     <row r="248" spans="1:26" x14ac:dyDescent="0.2">
@@ -14453,42 +14438,42 @@
         <v>0</v>
       </c>
       <c r="L248">
-        <f>$AJ$22</f>
-        <v>2</v>
+        <f>$AJ$18</f>
+        <v>2.5</v>
       </c>
       <c r="N248">
-        <f>$AJ$50</f>
-        <v>0.55000000000000004</v>
+        <f>$AJ$46</f>
+        <v>0.61</v>
       </c>
       <c r="O248">
         <f t="shared" si="69"/>
-        <v>0.43585000000000007</v>
+        <v>0.48354999999999998</v>
       </c>
       <c r="Q248">
-        <f>$AJ$77</f>
-        <v>50</v>
+        <f>$AJ$73</f>
+        <v>51</v>
       </c>
       <c r="R248">
         <f t="shared" si="76"/>
-        <v>0.8646283676396137</v>
+        <v>0.97873546256970145</v>
       </c>
       <c r="S248">
         <f t="shared" si="70"/>
-        <v>0.99966453737209748</v>
+        <v>0.99999627334682795</v>
       </c>
       <c r="T248">
         <v>1</v>
       </c>
       <c r="U248">
         <f t="shared" si="71"/>
-        <v>0.86433831713524623</v>
+        <v>0.97873181516208529</v>
       </c>
       <c r="V248">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="W248">
         <f t="shared" si="72"/>
-        <v>1.782956036214263E-2</v>
+        <v>1.9980158125047207E-2</v>
       </c>
       <c r="Y248">
         <f t="shared" si="73"/>
@@ -14496,7 +14481,7 @@
       </c>
       <c r="Z248">
         <f t="shared" si="74"/>
-        <v>48.808421491365451</v>
+        <v>100.27541859008066</v>
       </c>
     </row>
     <row r="249" spans="1:26" x14ac:dyDescent="0.2">
@@ -14513,42 +14498,42 @@
         <v>0</v>
       </c>
       <c r="L249">
-        <f>$AJ$23</f>
-        <v>2.2000000000000002</v>
+        <f>$AJ$19</f>
+        <v>1.6</v>
       </c>
       <c r="N249">
-        <f>$AJ$51</f>
-        <v>0.59</v>
+        <f>$AJ$47</f>
+        <v>0.64</v>
       </c>
       <c r="O249">
         <f t="shared" si="69"/>
-        <v>0.46765000000000001</v>
+        <v>0.50740000000000007</v>
       </c>
       <c r="Q249">
-        <f>$AJ$78</f>
+        <f>$AJ$74</f>
         <v>50</v>
       </c>
       <c r="R249">
         <f t="shared" si="76"/>
-        <v>0.92723225551115063</v>
+        <v>1.0054871153505722</v>
       </c>
       <c r="S249">
         <f t="shared" si="70"/>
-        <v>0.99993747849622516</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T249">
         <v>1</v>
       </c>
       <c r="U249">
         <f t="shared" si="71"/>
-        <v>0.92717428355618758</v>
+        <v>0.99947830132860371</v>
       </c>
       <c r="V249">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="W249">
         <f t="shared" si="72"/>
-        <v>1.9010876530856327E-2</v>
+        <v>2.0370192064977751E-2</v>
       </c>
       <c r="Y249">
         <f t="shared" si="73"/>
@@ -14556,7 +14541,7 @@
       </c>
       <c r="Z249">
         <f t="shared" si="74"/>
-        <v>43.368562086015991</v>
+        <v>83.645101166814896</v>
       </c>
     </row>
     <row r="250" spans="1:26" x14ac:dyDescent="0.2">
@@ -14572,43 +14557,45 @@
       <c r="I250">
         <v>0</v>
       </c>
-      <c r="L250">
-        <f>$AJ$24</f>
-        <v>1.7</v>
+      <c r="K250" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="L250" s="2">
+        <v>1.8</v>
       </c>
       <c r="N250">
-        <f>$AJ$52</f>
-        <v>0.57999999999999996</v>
+        <f>$AJ$48</f>
+        <v>0.72</v>
       </c>
       <c r="O250">
         <f t="shared" si="69"/>
-        <v>0.4597</v>
+        <v>0.57100000000000006</v>
       </c>
       <c r="Q250">
-        <f>$AJ$79</f>
-        <v>48</v>
+        <f>$AJ$75</f>
+        <v>51</v>
       </c>
       <c r="R250">
         <f t="shared" si="76"/>
-        <v>0.87289783757888828</v>
+        <v>1.1534721617679149</v>
       </c>
       <c r="S250">
         <f t="shared" si="70"/>
-        <v>0.99691128459176326</v>
+        <v>0.99846618932067555</v>
       </c>
       <c r="T250">
         <v>1</v>
       </c>
       <c r="U250">
         <f t="shared" si="71"/>
-        <v>0.87020170457814183</v>
+        <v>1.1517029538478918</v>
       </c>
       <c r="V250">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="W250">
         <f t="shared" si="72"/>
-        <v>1.7939792046069068E-2</v>
+        <v>2.3232015532340368E-2</v>
       </c>
       <c r="Y250">
         <f t="shared" si="73"/>
@@ -14616,7 +14603,7 @@
       </c>
       <c r="Z250">
         <f t="shared" si="74"/>
-        <v>32.740120484076051</v>
+        <v>84.796856693042344</v>
       </c>
     </row>
     <row r="251" spans="1:26" x14ac:dyDescent="0.2">
@@ -14639,42 +14626,42 @@
         <v>0</v>
       </c>
       <c r="L251">
-        <f>$AK$21</f>
-        <v>1.5</v>
+        <f>$AK$17</f>
+        <v>2.9</v>
       </c>
       <c r="N251">
-        <f>$AK$49</f>
-        <v>0.51</v>
+        <f>$AK$45</f>
+        <v>0.75</v>
       </c>
       <c r="O251">
         <f t="shared" si="69"/>
-        <v>0.40405000000000002</v>
+        <v>0.5948500000000001</v>
       </c>
       <c r="Q251">
-        <f>$AK$76</f>
+        <f>$AK$72</f>
         <v>20</v>
       </c>
       <c r="R251">
         <f t="shared" si="76"/>
-        <v>0.31629415472458533</v>
+        <v>0.5052226861752882</v>
       </c>
       <c r="S251">
         <f t="shared" si="70"/>
-        <v>0.98889100346175773</v>
+        <v>0.9999999504359468</v>
       </c>
       <c r="T251">
         <v>1</v>
       </c>
       <c r="U251">
         <f t="shared" si="71"/>
-        <v>0.31278044405468364</v>
+        <v>0.50522266113440406</v>
       </c>
       <c r="V251">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="W251">
         <f t="shared" si="72"/>
-        <v>7.4602723482280527E-3</v>
+        <v>1.1078186029326796E-2</v>
       </c>
       <c r="Y251">
         <f t="shared" si="73"/>
@@ -14682,7 +14669,7 @@
       </c>
       <c r="Z251">
         <f t="shared" si="74"/>
-        <v>10.211247776637148</v>
+        <v>30.326534255282102</v>
       </c>
     </row>
     <row r="252" spans="1:26" x14ac:dyDescent="0.2">
@@ -14699,42 +14686,42 @@
         <v>0</v>
       </c>
       <c r="L252">
-        <f>$AK$22</f>
-        <v>2</v>
+        <f>$AK$18</f>
+        <v>2.5</v>
       </c>
       <c r="N252">
-        <f>$AK$50</f>
-        <v>0.55000000000000004</v>
+        <f>$AK$46</f>
+        <v>0.61</v>
       </c>
       <c r="O252">
         <f t="shared" si="69"/>
-        <v>0.43585000000000007</v>
+        <v>0.48354999999999998</v>
       </c>
       <c r="Q252">
-        <f>$AK$77</f>
-        <v>25</v>
+        <f>$AK$73</f>
+        <v>27</v>
       </c>
       <c r="R252">
         <f t="shared" si="76"/>
-        <v>0.42830199467855401</v>
+        <v>0.52017847077168489</v>
       </c>
       <c r="S252">
         <f t="shared" si="70"/>
-        <v>0.99966453737209748</v>
+        <v>0.99999627334682795</v>
       </c>
       <c r="T252">
         <v>1</v>
       </c>
       <c r="U252">
         <f t="shared" si="71"/>
-        <v>0.42815831536588328</v>
+        <v>0.52017653224693672</v>
       </c>
       <c r="V252">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="W252">
         <f t="shared" si="72"/>
-        <v>9.6293763288786052E-3</v>
+        <v>1.135931880624241E-2</v>
       </c>
       <c r="Y252">
         <f t="shared" si="73"/>
@@ -14742,7 +14729,7 @@
       </c>
       <c r="Z252">
         <f t="shared" si="74"/>
-        <v>39.540626550457773</v>
+        <v>93.288405696265798</v>
       </c>
     </row>
     <row r="253" spans="1:26" x14ac:dyDescent="0.2">
@@ -14759,42 +14746,42 @@
         <v>0</v>
       </c>
       <c r="L253">
-        <f>$AK$23</f>
-        <v>2.2000000000000002</v>
+        <f>$AK$19</f>
+        <v>1.6</v>
       </c>
       <c r="N253">
-        <f>$AK$51</f>
-        <v>0.59</v>
+        <f>$AK$47</f>
+        <v>0.64</v>
       </c>
       <c r="O253">
         <f t="shared" si="69"/>
-        <v>0.46765000000000001</v>
+        <v>0.50740000000000007</v>
       </c>
       <c r="Q253">
-        <f>$AK$78</f>
-        <v>20</v>
+        <f>$AK$74</f>
+        <v>32</v>
       </c>
       <c r="R253">
         <f t="shared" si="76"/>
-        <v>0.37927033187481962</v>
+        <v>0.64511931548462409</v>
       </c>
       <c r="S253">
         <f t="shared" si="70"/>
-        <v>0.99993747849622516</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T253">
         <v>1</v>
       </c>
       <c r="U253">
         <f t="shared" si="71"/>
-        <v>0.37924661932333364</v>
+        <v>0.64126406768527744</v>
       </c>
       <c r="V253">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="W253">
         <f t="shared" si="72"/>
-        <v>8.7098364432786728E-3</v>
+        <v>1.3635764472483216E-2</v>
       </c>
       <c r="Y253">
         <f t="shared" si="73"/>
@@ -14802,7 +14789,7 @@
       </c>
       <c r="Z253">
         <f t="shared" si="74"/>
-        <v>31.790903017967157</v>
+        <v>99.54108064912748</v>
       </c>
     </row>
     <row r="254" spans="1:26" x14ac:dyDescent="0.2">
@@ -14818,43 +14805,45 @@
       <c r="I254">
         <v>0</v>
       </c>
-      <c r="L254">
-        <f>$AK$24</f>
-        <v>1.7</v>
+      <c r="K254" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="L254" s="2">
+        <v>1.6</v>
       </c>
       <c r="N254">
-        <f>$AK$52</f>
-        <v>0.57999999999999996</v>
+        <f>$AK$48</f>
+        <v>0.72</v>
       </c>
       <c r="O254">
         <f t="shared" si="69"/>
-        <v>0.4597</v>
+        <v>0.57100000000000006</v>
       </c>
       <c r="Q254">
-        <f>$AK$79</f>
-        <v>25</v>
+        <f>$AK$75</f>
+        <v>34</v>
       </c>
       <c r="R254">
         <f t="shared" si="76"/>
-        <v>0.45622036550992806</v>
+        <v>0.77753323213623582</v>
       </c>
       <c r="S254">
         <f t="shared" si="70"/>
-        <v>0.99691128459176326</v>
+        <v>0.99402397710499402</v>
       </c>
       <c r="T254">
         <v>1</v>
       </c>
       <c r="U254">
         <f t="shared" si="71"/>
-        <v>0.45481123063742612</v>
+        <v>0.77288667573936165</v>
       </c>
       <c r="V254">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="W254">
         <f t="shared" si="72"/>
-        <v>1.0130451135983612E-2</v>
+        <v>1.6110269503900002E-2</v>
       </c>
       <c r="Y254">
         <f t="shared" si="73"/>
@@ -14862,18 +14851,18 @@
       </c>
       <c r="Z254">
         <f t="shared" si="74"/>
-        <v>27.732109984755141</v>
+        <v>102.90434645616126</v>
       </c>
     </row>
     <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B261" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C261" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D261" t="s">
         <v>72</v>
@@ -14891,44 +14880,44 @@
         <v>0</v>
       </c>
       <c r="L261">
-        <f>$AF$25</f>
-        <v>4</v>
-      </c>
-      <c r="N261">
-        <f>$AF$53</f>
-        <v>0.7</v>
+        <f>$AF$21</f>
+        <v>1.5</v>
+      </c>
+      <c r="M261" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N261" s="2">
+        <v>0.5</v>
       </c>
       <c r="O261">
         <f>(0.795 * N261) - 0.0014</f>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="P261" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q261" s="2">
-        <v>79</v>
+        <v>0.39610000000000001</v>
+      </c>
+      <c r="Q261">
+        <f>$AF$76</f>
+        <v>58</v>
       </c>
       <c r="R261">
         <f>(104.7 * O261 + 0.307 * Q261- 15) * POWER(Q261, 0.75) * 10^-3</f>
-        <v>1.7852521511708519</v>
+        <v>0.93058437094840885</v>
       </c>
       <c r="S261">
         <f>1-EXP(-2*POWER(L261,2))</f>
-        <v>0.99999999999998734</v>
+        <v>0.98889100346175773</v>
       </c>
       <c r="T261">
         <v>1</v>
       </c>
       <c r="U261">
         <f>R261 * S261 * T261</f>
-        <v>1.7852521511708292</v>
+        <v>0.92024651239300059</v>
       </c>
       <c r="V261">
         <v>25</v>
       </c>
       <c r="W261">
         <f>(U261 * 0.0188) + 0.00158</f>
-        <v>3.5142740442011593E-2</v>
+        <v>1.8880634432988413E-2</v>
       </c>
       <c r="Y261">
         <f>$AF$4</f>
@@ -14936,11 +14925,11 @@
       </c>
       <c r="Z261">
         <f>V261*W261*Y261</f>
-        <v>80.169376633338942</v>
+        <v>43.071447300254817</v>
       </c>
       <c r="AA261">
         <f>SUM(Z261:Z284)*10^-3</f>
-        <v>2.1235281477198638</v>
+        <v>1.3279574495523139</v>
       </c>
     </row>
     <row r="262" spans="1:27" x14ac:dyDescent="0.2">
@@ -14957,44 +14946,44 @@
         <v>0</v>
       </c>
       <c r="L262">
-        <f>$AF$26</f>
-        <v>2.5</v>
-      </c>
-      <c r="N262">
-        <f>$AF$54</f>
-        <v>0.55000000000000004</v>
+        <f>$AF$22</f>
+        <v>2</v>
+      </c>
+      <c r="M262" s="2">
+        <v>0.51</v>
+      </c>
+      <c r="N262" s="2">
+        <v>0.51</v>
       </c>
       <c r="O262">
         <f t="shared" ref="O262:O284" si="79">(0.795 * N262) - 0.0014</f>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P262" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q262" s="2">
-        <v>78</v>
+        <v>0.40405000000000002</v>
+      </c>
+      <c r="Q262">
+        <f>$AF$77</f>
+        <v>61</v>
       </c>
       <c r="R262">
         <f>(104.7 * O262 + 0.307 * Q262- 15) * POWER(Q262, 0.75) * 10^-3</f>
-        <v>1.4325192446096717</v>
+        <v>1.0047270997102939</v>
       </c>
       <c r="S262">
         <f t="shared" ref="S262:S284" si="80">1-EXP(-2*POWER(L262,2))</f>
-        <v>0.99999627334682795</v>
+        <v>0.99966453737209748</v>
       </c>
       <c r="T262">
         <v>1</v>
       </c>
       <c r="U262">
         <f t="shared" ref="U262:U284" si="81">R262 * S262 * T262</f>
-        <v>1.4325139061072847</v>
+        <v>1.0043900513171002</v>
       </c>
       <c r="V262">
         <v>20</v>
       </c>
       <c r="W262">
         <f t="shared" ref="W262:W284" si="82">(U262 * 0.0188) + 0.00158</f>
-        <v>2.8511261434816956E-2</v>
+        <v>2.0462532964761488E-2</v>
       </c>
       <c r="Y262">
         <f t="shared" ref="Y262:Y284" si="83">$AF$4</f>
@@ -15002,7 +14991,7 @@
       </c>
       <c r="Z262">
         <f t="shared" ref="Z262:Z284" si="84">V262*W262*Y262</f>
-        <v>52.033052118540951</v>
+        <v>37.344122660689713</v>
       </c>
     </row>
     <row r="263" spans="1:27" x14ac:dyDescent="0.2">
@@ -15019,44 +15008,44 @@
         <v>0</v>
       </c>
       <c r="L263">
-        <f>$AF$27</f>
-        <v>0.7</v>
-      </c>
-      <c r="N263">
-        <f>$AF$55</f>
-        <v>0.55000000000000004</v>
+        <f>$AF$23</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M263" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="N263" s="2">
+        <v>0.52</v>
       </c>
       <c r="O263">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P263" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q263" s="2">
-        <v>77</v>
+        <v>0.41200000000000003</v>
+      </c>
+      <c r="Q263">
+        <f>$AF$78</f>
+        <v>63</v>
       </c>
       <c r="R263">
         <f t="shared" ref="R263:R268" si="85">(104.7 * O263 + 0.307 * Q263- 15) * POWER(Q263, 0.75) * 10^-3</f>
-        <v>1.4107427634270284</v>
+        <v>1.0616768308982532</v>
       </c>
       <c r="S263">
         <f t="shared" si="80"/>
-        <v>0.62468890114860043</v>
+        <v>0.99993747849622516</v>
       </c>
       <c r="T263">
         <v>1</v>
       </c>
       <c r="U263">
         <f t="shared" si="81"/>
-        <v>0.88127534668857033</v>
+        <v>1.0616104532662625</v>
       </c>
       <c r="V263">
         <v>19</v>
       </c>
       <c r="W263">
         <f t="shared" si="82"/>
-        <v>1.8147976517745124E-2</v>
+        <v>2.1538276521405737E-2</v>
       </c>
       <c r="Y263">
         <f t="shared" si="83"/>
@@ -15064,7 +15053,7 @@
       </c>
       <c r="Z263">
         <f t="shared" si="84"/>
-        <v>31.464054287640607</v>
+        <v>37.341986918987196</v>
       </c>
     </row>
     <row r="264" spans="1:27" x14ac:dyDescent="0.2">
@@ -15081,44 +15070,44 @@
         <v>0</v>
       </c>
       <c r="L264">
-        <f>$AF$28</f>
-        <v>0.9</v>
-      </c>
-      <c r="N264">
-        <f>$AF$56</f>
-        <v>0.75</v>
+        <f>$AF$24</f>
+        <v>1.7</v>
+      </c>
+      <c r="M264" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="N264" s="2">
+        <v>0.53</v>
       </c>
       <c r="O264">
         <f t="shared" si="79"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="P264" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q264" s="2">
-        <v>76</v>
+        <v>0.41995000000000005</v>
+      </c>
+      <c r="Q264">
+        <f>$AF$79</f>
+        <v>60</v>
       </c>
       <c r="R264">
         <f t="shared" si="85"/>
-        <v>1.8175802556295724</v>
+        <v>1.0216186875211368</v>
       </c>
       <c r="S264">
         <f t="shared" si="80"/>
-        <v>0.80210130091638532</v>
+        <v>0.99691128459176326</v>
       </c>
       <c r="T264">
         <v>1</v>
       </c>
       <c r="U264">
         <f t="shared" si="81"/>
-        <v>1.4578834875604161</v>
+        <v>1.0184631981396477</v>
       </c>
       <c r="V264">
         <v>25</v>
       </c>
       <c r="W264">
         <f t="shared" si="82"/>
-        <v>2.8988209566135827E-2</v>
+        <v>2.072710812502538E-2</v>
       </c>
       <c r="Y264">
         <f t="shared" si="83"/>
@@ -15126,7 +15115,7 @@
       </c>
       <c r="Z264">
         <f t="shared" si="84"/>
-        <v>66.12935307274735</v>
+        <v>47.28371541021415</v>
       </c>
     </row>
     <row r="265" spans="1:27" x14ac:dyDescent="0.2">
@@ -15149,44 +15138,44 @@
         <v>0</v>
       </c>
       <c r="L265">
-        <f>$AG$25</f>
-        <v>4</v>
-      </c>
-      <c r="N265">
-        <f>$AG$53</f>
-        <v>0.7</v>
+        <f>$AG$21</f>
+        <v>1.5</v>
+      </c>
+      <c r="M265" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N265" s="2">
+        <v>0.5</v>
       </c>
       <c r="O265">
         <f t="shared" si="79"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="P265" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q265" s="2">
-        <v>75</v>
+        <v>0.39610000000000001</v>
+      </c>
+      <c r="Q265">
+        <f>$AG$76</f>
+        <v>50</v>
       </c>
       <c r="R265">
         <f t="shared" si="85"/>
-        <v>1.6857229733976102</v>
+        <v>0.78637350780019211</v>
       </c>
       <c r="S265">
         <f t="shared" si="80"/>
-        <v>0.99999999999998734</v>
+        <v>0.98889100346175773</v>
       </c>
       <c r="T265">
         <v>1</v>
       </c>
       <c r="U265">
         <f t="shared" si="81"/>
-        <v>1.6857229733975889</v>
+        <v>0.7776376872242744</v>
       </c>
       <c r="V265">
         <v>50</v>
       </c>
       <c r="W265">
         <f t="shared" si="82"/>
-        <v>3.3271591899874671E-2</v>
+        <v>1.6199588519816361E-2</v>
       </c>
       <c r="Y265">
         <f t="shared" si="83"/>
@@ -15194,7 +15183,7 @@
       </c>
       <c r="Z265">
         <f t="shared" si="84"/>
-        <v>151.80163804317817</v>
+        <v>73.910622621662142</v>
       </c>
     </row>
     <row r="266" spans="1:27" x14ac:dyDescent="0.2">
@@ -15211,44 +15200,44 @@
         <v>0</v>
       </c>
       <c r="L266">
-        <f>$AG$26</f>
-        <v>2.5</v>
-      </c>
-      <c r="N266">
-        <f>$AG$54</f>
-        <v>0.55000000000000004</v>
+        <f>$AG$22</f>
+        <v>2</v>
+      </c>
+      <c r="M266" s="2">
+        <v>0.51</v>
+      </c>
+      <c r="N266" s="2">
+        <v>0.51</v>
       </c>
       <c r="O266">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P266" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q266" s="2">
-        <v>74</v>
+        <v>0.40405000000000002</v>
+      </c>
+      <c r="Q266">
+        <f>$AG$77</f>
+        <v>55</v>
       </c>
       <c r="R266">
         <f t="shared" si="85"/>
-        <v>1.3460784869379241</v>
+        <v>0.89245542667763567</v>
       </c>
       <c r="S266">
         <f t="shared" si="80"/>
-        <v>0.99999627334682795</v>
+        <v>0.99966453737209748</v>
       </c>
       <c r="T266">
         <v>1</v>
       </c>
       <c r="U266">
         <f t="shared" si="81"/>
-        <v>1.3460734705702608</v>
+        <v>0.89215604123491654</v>
       </c>
       <c r="V266">
         <v>60</v>
       </c>
       <c r="W266">
         <f t="shared" si="82"/>
-        <v>2.6886181246720906E-2</v>
+        <v>1.8352533575216434E-2</v>
       </c>
       <c r="Y266">
         <f t="shared" si="83"/>
@@ -15256,7 +15245,7 @@
       </c>
       <c r="Z266">
         <f t="shared" si="84"/>
-        <v>147.20184232579695</v>
+        <v>100.48012132430998</v>
       </c>
     </row>
     <row r="267" spans="1:27" x14ac:dyDescent="0.2">
@@ -15273,44 +15262,44 @@
         <v>0</v>
       </c>
       <c r="L267">
-        <f>$AG$27</f>
-        <v>0.7</v>
-      </c>
-      <c r="N267">
-        <f>$AG$55</f>
-        <v>0.55000000000000004</v>
+        <f>$AG$23</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M267" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="N267" s="2">
+        <v>0.52</v>
       </c>
       <c r="O267">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P267" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q267" s="2">
-        <v>73</v>
+        <v>0.41200000000000003</v>
+      </c>
+      <c r="Q267">
+        <f>$AG$78</f>
+        <v>55</v>
       </c>
       <c r="R267">
         <f t="shared" si="85"/>
-        <v>1.3247455344549881</v>
+        <v>0.90926612782163052</v>
       </c>
       <c r="S267">
         <f t="shared" si="80"/>
-        <v>0.62468890114860043</v>
+        <v>0.99993747849622516</v>
       </c>
       <c r="T267">
         <v>1</v>
       </c>
       <c r="U267">
         <f t="shared" si="81"/>
-        <v>0.82755383222020196</v>
+        <v>0.90920927913598759</v>
       </c>
       <c r="V267">
         <v>55</v>
       </c>
       <c r="W267">
         <f t="shared" si="82"/>
-        <v>1.7138012045739798E-2</v>
+        <v>1.8673134447756569E-2</v>
       </c>
       <c r="Y267">
         <f t="shared" si="83"/>
@@ -15318,7 +15307,7 @@
       </c>
       <c r="Z267">
         <f t="shared" si="84"/>
-        <v>86.011397954556614</v>
+        <v>93.715793509678278</v>
       </c>
     </row>
     <row r="268" spans="1:27" x14ac:dyDescent="0.2">
@@ -15335,44 +15324,44 @@
         <v>0</v>
       </c>
       <c r="L268">
-        <f>$AG$28</f>
-        <v>0.9</v>
-      </c>
-      <c r="N268">
-        <f>$AG$56</f>
-        <v>0.75</v>
+        <f>$AG$24</f>
+        <v>1.7</v>
+      </c>
+      <c r="M268" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="N268" s="2">
+        <v>0.53</v>
       </c>
       <c r="O268">
         <f t="shared" si="79"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="P268" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q268" s="2">
-        <v>72</v>
+        <v>0.41995000000000005</v>
+      </c>
+      <c r="Q268">
+        <f>$AG$79</f>
+        <v>50</v>
       </c>
       <c r="R268">
         <f t="shared" si="85"/>
-        <v>1.71499825233277</v>
+        <v>0.83332642370384502</v>
       </c>
       <c r="S268">
         <f t="shared" si="80"/>
-        <v>0.80210130091638532</v>
+        <v>0.99691128459176326</v>
       </c>
       <c r="T268">
         <v>1</v>
       </c>
       <c r="U268">
         <f t="shared" si="81"/>
-        <v>1.375602329265442</v>
+        <v>0.83075251553886009</v>
       </c>
       <c r="V268">
         <v>55</v>
       </c>
       <c r="W268">
         <f t="shared" si="82"/>
-        <v>2.7441323790190313E-2</v>
+        <v>1.719814729213057E-2</v>
       </c>
       <c r="Y268">
         <f t="shared" si="83"/>
@@ -15380,7 +15369,7 @@
       </c>
       <c r="Z268">
         <f t="shared" si="84"/>
-        <v>137.72114377201763</v>
+        <v>86.313201722380299</v>
       </c>
     </row>
     <row r="269" spans="1:27" x14ac:dyDescent="0.2">
@@ -15408,30 +15397,30 @@
         <v>1.3</v>
       </c>
       <c r="L269">
-        <f>$AH$25</f>
-        <v>4</v>
-      </c>
-      <c r="N269">
-        <f>$AH$53</f>
-        <v>0.7</v>
+        <f>$AH$21</f>
+        <v>1.5</v>
+      </c>
+      <c r="M269" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="N269" s="2">
+        <v>0.53</v>
       </c>
       <c r="O269">
         <f t="shared" si="79"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="P269" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q269" s="2">
-        <v>71</v>
+        <v>0.41995000000000005</v>
+      </c>
+      <c r="Q269">
+        <f>$AH$76</f>
+        <v>35</v>
       </c>
       <c r="R269">
         <f>(104.7 * O269 + 0.307 * Q269- 15) * POWER(Q269, 0.75) * 10^-3</f>
-        <v>1.5877982261232466</v>
+        <v>0.57146823458155449</v>
       </c>
       <c r="S269">
         <f t="shared" si="80"/>
-        <v>0.99999999999998734</v>
+        <v>0.98889100346175773</v>
       </c>
       <c r="T269">
         <f>(I269 * J269) + (1 - I269)</f>
@@ -15439,14 +15428,14 @@
       </c>
       <c r="U269">
         <f t="shared" si="81"/>
-        <v>1.9690603361799357</v>
+        <v>0.70081636134343506</v>
       </c>
       <c r="V269">
         <v>60</v>
       </c>
       <c r="W269">
         <f t="shared" si="82"/>
-        <v>3.8598334320182788E-2</v>
+        <v>1.475534759325658E-2</v>
       </c>
       <c r="Y269">
         <f t="shared" si="83"/>
@@ -15454,7 +15443,7 @@
       </c>
       <c r="Z269">
         <f t="shared" si="84"/>
-        <v>211.32588040300078</v>
+        <v>80.785528073079774</v>
       </c>
     </row>
     <row r="270" spans="1:27" x14ac:dyDescent="0.2">
@@ -15472,30 +15461,30 @@
         <v>0</v>
       </c>
       <c r="L270">
-        <f>$AH$26</f>
-        <v>2.5</v>
-      </c>
-      <c r="N270">
-        <f>$AH$54</f>
-        <v>0.55000000000000004</v>
+        <f>$AH$22</f>
+        <v>2</v>
+      </c>
+      <c r="M270" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="N270" s="2">
+        <v>0.53</v>
       </c>
       <c r="O270">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P270" s="2">
-        <v>70</v>
-      </c>
-      <c r="Q270" s="2">
-        <v>70</v>
+        <v>0.41995000000000005</v>
+      </c>
+      <c r="Q270">
+        <f>$AH$77</f>
+        <v>40</v>
       </c>
       <c r="R270">
         <f t="shared" ref="R270:R284" si="86">(104.7 * O270 + 0.307 * Q270- 15) * POWER(Q270, 0.75) * 10^-3</f>
-        <v>1.2614122912776211</v>
+        <v>0.65607870804581636</v>
       </c>
       <c r="S270">
         <f t="shared" si="80"/>
-        <v>0.99999627334682795</v>
+        <v>0.99966453737209748</v>
       </c>
       <c r="T270">
         <f t="shared" ref="T270:T276" si="87">(I270 * J270) + (1 - I270)</f>
@@ -15503,14 +15492,14 @@
       </c>
       <c r="U270">
         <f t="shared" si="81"/>
-        <v>1.2614075904315045</v>
+        <v>0.65585861815830437</v>
       </c>
       <c r="V270">
         <v>70</v>
       </c>
       <c r="W270">
         <f t="shared" si="82"/>
-        <v>2.5294462700112288E-2</v>
+        <v>1.3910142021376122E-2</v>
       </c>
       <c r="Y270">
         <f t="shared" si="83"/>
@@ -15518,7 +15507,7 @@
       </c>
       <c r="Z270">
         <f t="shared" si="84"/>
-        <v>161.56838049696725</v>
+        <v>88.851032161539976</v>
       </c>
     </row>
     <row r="271" spans="1:27" x14ac:dyDescent="0.2">
@@ -15536,30 +15525,30 @@
         <v>0</v>
       </c>
       <c r="L271">
-        <f>$AH$27</f>
-        <v>0.7</v>
-      </c>
-      <c r="N271">
-        <f>$AH$55</f>
-        <v>0.55000000000000004</v>
+        <f>$AH$23</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M271" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="N271" s="2">
+        <v>0.53</v>
       </c>
       <c r="O271">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P271" s="2">
-        <v>69</v>
-      </c>
-      <c r="Q271" s="2">
-        <v>69</v>
+        <v>0.41995000000000005</v>
+      </c>
+      <c r="Q271">
+        <f>$AH$78</f>
+        <v>40</v>
       </c>
       <c r="R271">
         <f t="shared" si="86"/>
-        <v>1.2405230861491703</v>
+        <v>0.65607870804581636</v>
       </c>
       <c r="S271">
         <f t="shared" si="80"/>
-        <v>0.62468890114860043</v>
+        <v>0.99993747849622516</v>
       </c>
       <c r="T271">
         <f t="shared" si="87"/>
@@ -15567,14 +15556,14 @@
       </c>
       <c r="U271">
         <f t="shared" si="81"/>
-        <v>0.77494100353599582</v>
+        <v>0.65603768901839465</v>
       </c>
       <c r="V271">
         <v>60</v>
       </c>
       <c r="W271">
         <f t="shared" si="82"/>
-        <v>1.6148890866476723E-2</v>
+        <v>1.391350855354582E-2</v>
       </c>
       <c r="Y271">
         <f t="shared" si="83"/>
@@ -15582,7 +15571,7 @@
       </c>
       <c r="Z271">
         <f t="shared" si="84"/>
-        <v>88.415177493960059</v>
+        <v>76.176459330663363</v>
       </c>
     </row>
     <row r="272" spans="1:27" x14ac:dyDescent="0.2">
@@ -15600,30 +15589,30 @@
         <v>0</v>
       </c>
       <c r="L272">
-        <f>$AH$28</f>
-        <v>0.9</v>
-      </c>
-      <c r="N272">
-        <f>$AH$56</f>
-        <v>0.75</v>
+        <f>$AH$24</f>
+        <v>1.7</v>
+      </c>
+      <c r="M272" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="N272" s="2">
+        <v>0.53</v>
       </c>
       <c r="O272">
         <f t="shared" si="79"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="P272" s="2">
-        <v>68</v>
-      </c>
-      <c r="Q272" s="2">
-        <v>68</v>
+        <v>0.41995000000000005</v>
+      </c>
+      <c r="Q272">
+        <f>$AH$79</f>
+        <v>35</v>
       </c>
       <c r="R272">
         <f t="shared" si="86"/>
-        <v>1.6139528553516362</v>
+        <v>0.57146823458155449</v>
       </c>
       <c r="S272">
         <f t="shared" si="80"/>
-        <v>0.80210130091638532</v>
+        <v>0.99691128459176326</v>
       </c>
       <c r="T272">
         <f t="shared" si="87"/>
@@ -15631,14 +15620,14 @@
       </c>
       <c r="U272">
         <f t="shared" si="81"/>
-        <v>1.2945536848952621</v>
+        <v>0.56970313184008459</v>
       </c>
       <c r="V272">
         <v>50</v>
       </c>
       <c r="W272">
         <f t="shared" si="82"/>
-        <v>2.5917609276030932E-2</v>
+        <v>1.2290418878593591E-2</v>
       </c>
       <c r="Y272">
         <f t="shared" si="83"/>
@@ -15646,7 +15635,7 @@
       </c>
       <c r="Z272">
         <f t="shared" si="84"/>
-        <v>118.24909232189113</v>
+        <v>56.075036133583261</v>
       </c>
     </row>
     <row r="273" spans="1:26" x14ac:dyDescent="0.2">
@@ -15674,30 +15663,28 @@
         <v>1.3</v>
       </c>
       <c r="L273">
-        <f>$AI$25</f>
-        <v>4</v>
+        <f>$AI$21</f>
+        <v>1.5</v>
       </c>
       <c r="N273">
-        <f>$AI$53</f>
-        <v>0.7</v>
+        <f>$AI$49</f>
+        <v>0.51</v>
       </c>
       <c r="O273">
         <f t="shared" si="79"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="P273" s="2">
-        <v>67</v>
-      </c>
-      <c r="Q273" s="2">
-        <v>67</v>
+        <v>0.40405000000000002</v>
+      </c>
+      <c r="Q273">
+        <f>$AI$76</f>
+        <v>40</v>
       </c>
       <c r="R273">
         <f t="shared" si="86"/>
-        <v>1.4914665181818776</v>
+        <v>0.62960048723980899</v>
       </c>
       <c r="S273">
         <f t="shared" si="80"/>
-        <v>0.99999999999998734</v>
+        <v>0.98889100346175773</v>
       </c>
       <c r="T273">
         <f t="shared" si="87"/>
@@ -15705,14 +15692,14 @@
       </c>
       <c r="U273">
         <f t="shared" si="81"/>
-        <v>1.8655263209418687</v>
+        <v>0.77875590701431807</v>
       </c>
       <c r="V273">
         <v>40</v>
       </c>
       <c r="W273">
         <f t="shared" si="82"/>
-        <v>3.6651894833707128E-2</v>
+        <v>1.6220611051869182E-2</v>
       </c>
       <c r="Y273">
         <f t="shared" si="83"/>
@@ -15720,7 +15707,7 @@
       </c>
       <c r="Z273">
         <f t="shared" si="84"/>
-        <v>133.779416143031</v>
+        <v>59.205230339322519</v>
       </c>
     </row>
     <row r="274" spans="1:26" x14ac:dyDescent="0.2">
@@ -15737,30 +15724,28 @@
         <v>0</v>
       </c>
       <c r="L274">
-        <f>$AI$26</f>
-        <v>2.5</v>
+        <f>$AI$22</f>
+        <v>2</v>
       </c>
       <c r="N274">
-        <f>$AI$54</f>
+        <f>$AI$50</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O274">
         <f t="shared" si="79"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="P274" s="2">
-        <v>66</v>
-      </c>
-      <c r="Q274" s="2">
-        <v>66</v>
+      <c r="Q274">
+        <f>$AI$77</f>
+        <v>45</v>
       </c>
       <c r="R274">
         <f t="shared" si="86"/>
-        <v>1.1785209149153895</v>
+        <v>0.77226516609487061</v>
       </c>
       <c r="S274">
         <f t="shared" si="80"/>
-        <v>0.99999627334682795</v>
+        <v>0.99966453737209748</v>
       </c>
       <c r="T274">
         <f t="shared" si="87"/>
@@ -15768,14 +15753,14 @@
       </c>
       <c r="U274">
         <f t="shared" si="81"/>
-        <v>1.1785165229766836</v>
+        <v>0.77200609999281489</v>
       </c>
       <c r="V274">
         <v>45</v>
       </c>
       <c r="W274">
         <f t="shared" si="82"/>
-        <v>2.3736110631961654E-2</v>
+        <v>1.609371467986492E-2</v>
       </c>
       <c r="Y274">
         <f t="shared" si="83"/>
@@ -15783,7 +15768,7 @@
       </c>
       <c r="Z274">
         <f t="shared" si="84"/>
-        <v>97.466404282492547</v>
+        <v>66.084815904195324</v>
       </c>
     </row>
     <row r="275" spans="1:26" x14ac:dyDescent="0.2">
@@ -15800,30 +15785,28 @@
         <v>0</v>
       </c>
       <c r="L275">
-        <f>$AI$27</f>
-        <v>0.7</v>
+        <f>$AI$23</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N275">
-        <f>$AI$55</f>
-        <v>0.55000000000000004</v>
+        <f>$AI$51</f>
+        <v>0.59</v>
       </c>
       <c r="O275">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P275" s="2">
-        <v>65</v>
-      </c>
-      <c r="Q275" s="2">
-        <v>65</v>
+        <v>0.46765000000000001</v>
+      </c>
+      <c r="Q275">
+        <f>$AI$78</f>
+        <v>45</v>
       </c>
       <c r="R275">
         <f t="shared" si="86"/>
-        <v>1.1580752413958724</v>
+        <v>0.8301124785833186</v>
       </c>
       <c r="S275">
         <f t="shared" si="80"/>
-        <v>0.62468890114860043</v>
+        <v>0.99993747849622516</v>
       </c>
       <c r="T275">
         <f t="shared" si="87"/>
@@ -15831,14 +15814,14 @@
       </c>
       <c r="U275">
         <f t="shared" si="81"/>
-        <v>0.72343674999498764</v>
+        <v>0.83006057870285532</v>
       </c>
       <c r="V275">
         <v>40</v>
       </c>
       <c r="W275">
         <f t="shared" si="82"/>
-        <v>1.5180610899905769E-2</v>
+        <v>1.7185138879613683E-2</v>
       </c>
       <c r="Y275">
         <f t="shared" si="83"/>
@@ -15846,7 +15829,7 @@
       </c>
       <c r="Z275">
         <f t="shared" si="84"/>
-        <v>55.409229784656056</v>
+        <v>62.725756910589936</v>
       </c>
     </row>
     <row r="276" spans="1:26" x14ac:dyDescent="0.2">
@@ -15863,30 +15846,28 @@
         <v>0</v>
       </c>
       <c r="L276">
-        <f>$AI$28</f>
-        <v>0.9</v>
+        <f>$AI$24</f>
+        <v>1.7</v>
       </c>
       <c r="N276">
-        <f>$AI$56</f>
-        <v>0.75</v>
+        <f>$AI$52</f>
+        <v>0.57999999999999996</v>
       </c>
       <c r="O276">
         <f t="shared" si="79"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="P276" s="2">
-        <v>64</v>
-      </c>
-      <c r="Q276" s="2">
-        <v>64</v>
+        <v>0.4597</v>
+      </c>
+      <c r="Q276">
+        <f>$AI$79</f>
+        <v>42</v>
       </c>
       <c r="R276">
         <f t="shared" si="86"/>
-        <v>1.5144257536366168</v>
+        <v>0.7593235966549482</v>
       </c>
       <c r="S276">
         <f t="shared" si="80"/>
-        <v>0.80210130091638532</v>
+        <v>0.99691128459176326</v>
       </c>
       <c r="T276">
         <f t="shared" si="87"/>
@@ -15894,14 +15875,14 @@
       </c>
       <c r="U276">
         <f t="shared" si="81"/>
-        <v>1.2147228671332075</v>
+        <v>0.75697826216212227</v>
       </c>
       <c r="V276">
         <v>35</v>
       </c>
       <c r="W276">
         <f t="shared" si="82"/>
-        <v>2.4416789902104306E-2</v>
+        <v>1.5811191328647899E-2</v>
       </c>
       <c r="Y276">
         <f t="shared" si="83"/>
@@ -15909,7 +15890,7 @@
       </c>
       <c r="Z276">
         <f t="shared" si="84"/>
-        <v>77.981122749845625</v>
+        <v>50.496992305869227</v>
       </c>
     </row>
     <row r="277" spans="1:26" x14ac:dyDescent="0.2">
@@ -15932,44 +15913,42 @@
         <v>0</v>
       </c>
       <c r="L277">
-        <f>$AJ$25</f>
-        <v>4</v>
+        <f>$AJ$21</f>
+        <v>1.5</v>
       </c>
       <c r="N277">
-        <f>$AJ$53</f>
-        <v>0.7</v>
+        <f>$AJ$49</f>
+        <v>0.51</v>
       </c>
       <c r="O277">
         <f t="shared" si="79"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="P277" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q277" s="2">
-        <v>63</v>
+        <v>0.40405000000000002</v>
+      </c>
+      <c r="Q277">
+        <f>$AJ$76</f>
+        <v>45</v>
       </c>
       <c r="R277">
         <f t="shared" si="86"/>
-        <v>1.3967130257259237</v>
+        <v>0.71441785360642229</v>
       </c>
       <c r="S277">
         <f t="shared" si="80"/>
-        <v>0.99999999999998734</v>
+        <v>0.98889100346175773</v>
       </c>
       <c r="T277">
         <v>1</v>
       </c>
       <c r="U277">
         <f t="shared" si="81"/>
-        <v>1.3967130257259059</v>
+        <v>0.70648138814385009</v>
       </c>
       <c r="V277">
         <v>25</v>
       </c>
       <c r="W277">
         <f t="shared" si="82"/>
-        <v>2.7838204883647036E-2</v>
+        <v>1.4861850097104381E-2</v>
       </c>
       <c r="Y277">
         <f t="shared" si="83"/>
@@ -15977,7 +15956,7 @@
       </c>
       <c r="Z277">
         <f t="shared" si="84"/>
-        <v>63.505904890819806</v>
+        <v>33.903595534019367</v>
       </c>
     </row>
     <row r="278" spans="1:26" x14ac:dyDescent="0.2">
@@ -15994,44 +15973,42 @@
         <v>0</v>
       </c>
       <c r="L278">
-        <f>$AJ$26</f>
-        <v>2.5</v>
+        <f>$AJ$22</f>
+        <v>2</v>
       </c>
       <c r="N278">
-        <f>$AJ$54</f>
+        <f>$AJ$50</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O278">
         <f t="shared" si="79"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="P278" s="2">
-        <v>62</v>
-      </c>
-      <c r="Q278" s="2">
-        <v>62</v>
+      <c r="Q278">
+        <f>$AJ$77</f>
+        <v>50</v>
       </c>
       <c r="R278">
         <f t="shared" si="86"/>
-        <v>1.0974026986740544</v>
+        <v>0.8646283676396137</v>
       </c>
       <c r="S278">
         <f t="shared" si="80"/>
-        <v>0.99999627334682795</v>
+        <v>0.99966453737209748</v>
       </c>
       <c r="T278">
         <v>1</v>
       </c>
       <c r="U278">
         <f t="shared" si="81"/>
-        <v>1.0973986090348062</v>
+        <v>0.86433831713524623</v>
       </c>
       <c r="V278">
         <v>30</v>
       </c>
       <c r="W278">
         <f t="shared" si="82"/>
-        <v>2.2211093849854358E-2</v>
+        <v>1.782956036214263E-2</v>
       </c>
       <c r="Y278">
         <f t="shared" si="83"/>
@@ -16039,7 +16016,7 @@
       </c>
       <c r="Z278">
         <f t="shared" si="84"/>
-        <v>60.802869413976303</v>
+        <v>48.808421491365451</v>
       </c>
     </row>
     <row r="279" spans="1:26" x14ac:dyDescent="0.2">
@@ -16056,44 +16033,42 @@
         <v>0</v>
       </c>
       <c r="L279">
-        <f>$AJ$27</f>
-        <v>0.7</v>
+        <f>$AJ$23</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N279">
-        <f>$AJ$55</f>
-        <v>0.55000000000000004</v>
+        <f>$AJ$51</f>
+        <v>0.59</v>
       </c>
       <c r="O279">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P279" s="2">
-        <v>61</v>
-      </c>
-      <c r="Q279" s="2">
-        <v>61</v>
+        <v>0.46765000000000001</v>
+      </c>
+      <c r="Q279">
+        <f>$AJ$78</f>
+        <v>50</v>
       </c>
       <c r="R279">
         <f t="shared" si="86"/>
-        <v>1.0773997799878814</v>
+        <v>0.92723225551115063</v>
       </c>
       <c r="S279">
         <f t="shared" si="80"/>
-        <v>0.62468890114860043</v>
+        <v>0.99993747849622516</v>
       </c>
       <c r="T279">
         <v>1</v>
       </c>
       <c r="U279">
         <f t="shared" si="81"/>
-        <v>0.67303968465837349</v>
+        <v>0.92717428355618758</v>
       </c>
       <c r="V279">
         <v>25</v>
       </c>
       <c r="W279">
         <f t="shared" si="82"/>
-        <v>1.4233146071577421E-2</v>
+        <v>1.9010876530856327E-2</v>
       </c>
       <c r="Y279">
         <f t="shared" si="83"/>
@@ -16101,7 +16076,7 @@
       </c>
       <c r="Z279">
         <f t="shared" si="84"/>
-        <v>32.469364475785987</v>
+        <v>43.368562086015991</v>
       </c>
     </row>
     <row r="280" spans="1:26" x14ac:dyDescent="0.2">
@@ -16118,44 +16093,42 @@
         <v>0</v>
       </c>
       <c r="L280">
-        <f>$AJ$28</f>
-        <v>0.9</v>
+        <f>$AJ$24</f>
+        <v>1.7</v>
       </c>
       <c r="N280">
-        <f>$AJ$56</f>
-        <v>0.75</v>
+        <f>$AJ$52</f>
+        <v>0.57999999999999996</v>
       </c>
       <c r="O280">
         <f t="shared" si="79"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="P280" s="2">
-        <v>60</v>
-      </c>
-      <c r="Q280" s="2">
-        <v>60</v>
+        <v>0.4597</v>
+      </c>
+      <c r="Q280">
+        <f>$AJ$79</f>
+        <v>48</v>
       </c>
       <c r="R280">
         <f t="shared" si="86"/>
-        <v>1.4163939481646182</v>
+        <v>0.87289783757888828</v>
       </c>
       <c r="S280">
         <f t="shared" si="80"/>
-        <v>0.80210130091638532</v>
+        <v>0.99691128459176326</v>
       </c>
       <c r="T280">
         <v>1</v>
       </c>
       <c r="U280">
         <f t="shared" si="81"/>
-        <v>1.1360914284329355</v>
+        <v>0.87020170457814183</v>
       </c>
       <c r="V280">
         <v>20</v>
       </c>
       <c r="W280">
         <f t="shared" si="82"/>
-        <v>2.2938518854539191E-2</v>
+        <v>1.7939792046069068E-2</v>
       </c>
       <c r="Y280">
         <f t="shared" si="83"/>
@@ -16163,7 +16136,7 @@
       </c>
       <c r="Z280">
         <f t="shared" si="84"/>
-        <v>41.862796909534026</v>
+        <v>32.740120484076051</v>
       </c>
     </row>
     <row r="281" spans="1:26" x14ac:dyDescent="0.2">
@@ -16186,44 +16159,42 @@
         <v>0</v>
       </c>
       <c r="L281">
-        <f>$AK$25</f>
-        <v>4</v>
+        <f>$AK$21</f>
+        <v>1.5</v>
       </c>
       <c r="N281">
-        <f>$AK$53</f>
-        <v>0.7</v>
+        <f>$AK$49</f>
+        <v>0.51</v>
       </c>
       <c r="O281">
         <f t="shared" si="79"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="P281" s="2">
-        <v>59</v>
-      </c>
-      <c r="Q281" s="2">
-        <v>59</v>
+        <v>0.40405000000000002</v>
+      </c>
+      <c r="Q281">
+        <f>$AK$76</f>
+        <v>20</v>
       </c>
       <c r="R281">
         <f t="shared" si="86"/>
-        <v>1.303518624930883</v>
+        <v>0.31629415472458533</v>
       </c>
       <c r="S281">
         <f t="shared" si="80"/>
-        <v>0.99999999999998734</v>
+        <v>0.98889100346175773</v>
       </c>
       <c r="T281">
         <v>1</v>
       </c>
       <c r="U281">
         <f t="shared" si="81"/>
-        <v>1.3035186249308666</v>
+        <v>0.31278044405468364</v>
       </c>
       <c r="V281">
         <v>15</v>
       </c>
       <c r="W281">
         <f t="shared" si="82"/>
-        <v>2.6086150148700294E-2</v>
+        <v>7.4602723482280527E-3</v>
       </c>
       <c r="Y281">
         <f t="shared" si="83"/>
@@ -16231,7 +16202,7 @@
       </c>
       <c r="Z281">
         <f t="shared" si="84"/>
-        <v>35.705418016033526</v>
+        <v>10.211247776637148</v>
       </c>
     </row>
     <row r="282" spans="1:26" x14ac:dyDescent="0.2">
@@ -16248,44 +16219,42 @@
         <v>0</v>
       </c>
       <c r="L282">
-        <f>$AK$26</f>
-        <v>2.5</v>
+        <f>$AK$22</f>
+        <v>2</v>
       </c>
       <c r="N282">
-        <f>$AK$54</f>
+        <f>$AK$50</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O282">
         <f t="shared" si="79"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="P282" s="2">
-        <v>58</v>
-      </c>
-      <c r="Q282" s="2">
-        <v>58</v>
+      <c r="Q282">
+        <f>$AK$77</f>
+        <v>25</v>
       </c>
       <c r="R282">
         <f t="shared" si="86"/>
-        <v>1.0180535015422809</v>
+        <v>0.42830199467855401</v>
       </c>
       <c r="S282">
         <f t="shared" si="80"/>
-        <v>0.99999627334682795</v>
+        <v>0.99966453737209748</v>
       </c>
       <c r="T282">
         <v>1</v>
       </c>
       <c r="U282">
         <f t="shared" si="81"/>
-        <v>1.0180497076099702</v>
+        <v>0.42815831536588328</v>
       </c>
       <c r="V282">
         <v>45</v>
       </c>
       <c r="W282">
         <f t="shared" si="82"/>
-        <v>2.0719334503067441E-2</v>
+        <v>9.6293763288786052E-3</v>
       </c>
       <c r="Y282">
         <f t="shared" si="83"/>
@@ -16293,7 +16262,7 @@
       </c>
       <c r="Z282">
         <f t="shared" si="84"/>
-        <v>85.078767303220687</v>
+        <v>39.540626550457773</v>
       </c>
     </row>
     <row r="283" spans="1:26" x14ac:dyDescent="0.2">
@@ -16310,44 +16279,42 @@
         <v>0</v>
       </c>
       <c r="L283">
-        <f>$AK$27</f>
-        <v>0.7</v>
+        <f>$AK$23</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N283">
-        <f>$AK$55</f>
-        <v>0.55000000000000004</v>
+        <f>$AK$51</f>
+        <v>0.59</v>
       </c>
       <c r="O283">
         <f t="shared" si="79"/>
-        <v>0.43585000000000007</v>
-      </c>
-      <c r="P283" s="2">
-        <v>57</v>
-      </c>
-      <c r="Q283" s="2">
-        <v>57</v>
+        <v>0.46765000000000001</v>
+      </c>
+      <c r="Q283">
+        <f>$AK$78</f>
+        <v>20</v>
       </c>
       <c r="R283">
         <f t="shared" si="86"/>
-        <v>0.99849183106675043</v>
+        <v>0.37927033187481962</v>
       </c>
       <c r="S283">
         <f t="shared" si="80"/>
-        <v>0.62468890114860043</v>
+        <v>0.99993747849622516</v>
       </c>
       <c r="T283">
         <v>1</v>
       </c>
       <c r="U283">
         <f t="shared" si="81"/>
-        <v>0.62374676475494228</v>
+        <v>0.37924661932333364</v>
       </c>
       <c r="V283">
         <v>40</v>
       </c>
       <c r="W283">
         <f t="shared" si="82"/>
-        <v>1.3306439177392914E-2</v>
+        <v>8.7098364432786728E-3</v>
       </c>
       <c r="Y283">
         <f t="shared" si="83"/>
@@ -16355,7 +16322,7 @@
       </c>
       <c r="Z283">
         <f t="shared" si="84"/>
-        <v>48.568502997484138</v>
+        <v>31.790903017967157</v>
       </c>
     </row>
     <row r="284" spans="1:26" x14ac:dyDescent="0.2">
@@ -16372,44 +16339,42 @@
         <v>0</v>
       </c>
       <c r="L284">
-        <f>$AK$28</f>
-        <v>0.9</v>
+        <f>$AK$24</f>
+        <v>1.7</v>
       </c>
       <c r="N284">
-        <f>$AK$56</f>
-        <v>0.75</v>
+        <f>$AK$52</f>
+        <v>0.57999999999999996</v>
       </c>
       <c r="O284">
         <f t="shared" si="79"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="P284" s="2">
-        <v>56</v>
-      </c>
-      <c r="Q284" s="2">
-        <v>56</v>
+        <v>0.4597</v>
+      </c>
+      <c r="Q284">
+        <f>$AK$79</f>
+        <v>25</v>
       </c>
       <c r="R284">
         <f t="shared" si="86"/>
-        <v>1.3198285488795851</v>
+        <v>0.45622036550992806</v>
       </c>
       <c r="S284">
         <f t="shared" si="80"/>
-        <v>0.80210130091638532</v>
+        <v>0.99691128459176326</v>
       </c>
       <c r="T284">
         <v>1</v>
       </c>
       <c r="U284">
         <f t="shared" si="81"/>
-        <v>1.0586361960429003</v>
+        <v>0.45481123063742612</v>
       </c>
       <c r="V284">
         <v>30</v>
       </c>
       <c r="W284">
         <f t="shared" si="82"/>
-        <v>2.1482360485606526E-2</v>
+        <v>1.0130451135983612E-2</v>
       </c>
       <c r="Y284">
         <f t="shared" si="83"/>
@@ -16417,18 +16382,18 @@
       </c>
       <c r="Z284">
         <f t="shared" si="84"/>
-        <v>58.807961829347867</v>
+        <v>27.732109984755141</v>
       </c>
     </row>
     <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B291" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C291" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D291" t="s">
         <v>72</v>
@@ -16446,42 +16411,44 @@
         <v>0</v>
       </c>
       <c r="L291">
-        <f>$AF$29</f>
-        <v>2.5</v>
+        <f>$AF$25</f>
+        <v>4</v>
       </c>
       <c r="N291">
-        <f>$AF$57</f>
-        <v>0.75</v>
+        <f>$AF$53</f>
+        <v>0.7</v>
       </c>
       <c r="O291">
         <f>(0.795 * N291) - 0.0014</f>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q291">
-        <f>$AF$84</f>
-        <v>90</v>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="P291" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q291" s="2">
+        <v>79</v>
       </c>
       <c r="R291">
         <f>(104.7 * O291 + 0.307 * Q291- 15) * POWER(Q291, 0.75) * 10^-3</f>
-        <v>2.188901849330922</v>
+        <v>1.7852521511708519</v>
       </c>
       <c r="S291">
         <f>1-EXP(-2*POWER(L291,2))</f>
-        <v>0.99999627334682795</v>
+        <v>0.99999999999998734</v>
       </c>
       <c r="T291">
         <v>1</v>
       </c>
       <c r="U291">
         <f>R291 * S291 * T291</f>
-        <v>2.1888936920529019</v>
+        <v>1.7852521511708292</v>
       </c>
       <c r="V291">
         <v>25</v>
       </c>
       <c r="W291">
         <f>(U291 * 0.0188) + 0.00158</f>
-        <v>4.2731201410594555E-2</v>
+        <v>3.5142740442011593E-2</v>
       </c>
       <c r="Y291">
         <f>$AF$4</f>
@@ -16489,11 +16456,11 @@
       </c>
       <c r="Z291">
         <f>V291*W291*Y291</f>
-        <v>97.480553217918825</v>
+        <v>80.169376633338942</v>
       </c>
       <c r="AA291">
         <f>SUM(Z291:Z314)*10^-3</f>
-        <v>1.732155183172819</v>
+        <v>2.1235281477198638</v>
       </c>
     </row>
     <row r="292" spans="1:27" x14ac:dyDescent="0.2">
@@ -16510,24 +16477,26 @@
         <v>0</v>
       </c>
       <c r="L292">
-        <f>$AF$30</f>
+        <f>$AF$26</f>
         <v>2.5</v>
       </c>
       <c r="N292">
-        <f>$AF$58</f>
+        <f>$AF$54</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O292">
         <f t="shared" ref="O292:O314" si="89">(0.795 * N292) - 0.0014</f>
         <v>0.43585000000000007</v>
       </c>
-      <c r="Q292">
-        <f>$AF$85</f>
-        <v>90</v>
+      <c r="P292" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q292" s="2">
+        <v>78</v>
       </c>
       <c r="R292">
         <f>(104.7 * O292 + 0.307 * Q292- 15) * POWER(Q292, 0.75) * 10^-3</f>
-        <v>1.7024658722949466</v>
+        <v>1.4325192446096717</v>
       </c>
       <c r="S292">
         <f t="shared" ref="S292:S314" si="90">1-EXP(-2*POWER(L292,2))</f>
@@ -16538,14 +16507,14 @@
       </c>
       <c r="U292">
         <f t="shared" ref="U292:U314" si="91">R292 * S292 * T292</f>
-        <v>1.7024595277951033</v>
+        <v>1.4325139061072847</v>
       </c>
       <c r="V292">
         <v>20</v>
       </c>
       <c r="W292">
         <f t="shared" ref="W292:W314" si="92">(U292 * 0.0188) + 0.00158</f>
-        <v>3.3586239122547941E-2</v>
+        <v>2.8511261434816956E-2</v>
       </c>
       <c r="Y292">
         <f t="shared" ref="Y292:Y314" si="93">$AF$4</f>
@@ -16553,7 +16522,7 @@
       </c>
       <c r="Z292">
         <f t="shared" ref="Z292:Z314" si="94">V292*W292*Y292</f>
-        <v>61.294886398649993</v>
+        <v>52.033052118540951</v>
       </c>
     </row>
     <row r="293" spans="1:27" x14ac:dyDescent="0.2">
@@ -16570,42 +16539,44 @@
         <v>0</v>
       </c>
       <c r="L293">
-        <f>$AF$31</f>
-        <v>1.3</v>
+        <f>$AF$27</f>
+        <v>0.7</v>
       </c>
       <c r="N293">
-        <f>$AF$59</f>
-        <v>0.67</v>
+        <f>$AF$55</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O293">
         <f t="shared" si="89"/>
-        <v>0.53125000000000011</v>
-      </c>
-      <c r="Q293">
-        <f>$AF$86</f>
-        <v>75</v>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="P293" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q293" s="2">
+        <v>77</v>
       </c>
       <c r="R293">
         <f t="shared" ref="R293:R298" si="95">(104.7 * O293 + 0.307 * Q293- 15) * POWER(Q293, 0.75) * 10^-3</f>
-        <v>1.6220828500688129</v>
+        <v>1.4107427634270284</v>
       </c>
       <c r="S293">
         <f t="shared" si="90"/>
-        <v>0.96595254526540064</v>
+        <v>0.62468890114860043</v>
       </c>
       <c r="T293">
         <v>1</v>
       </c>
       <c r="U293">
         <f t="shared" si="91"/>
-        <v>1.5668550576553251</v>
+        <v>0.88127534668857033</v>
       </c>
       <c r="V293">
         <v>19</v>
       </c>
       <c r="W293">
         <f t="shared" si="92"/>
-        <v>3.1036875083920112E-2</v>
+        <v>1.8147976517745124E-2</v>
       </c>
       <c r="Y293">
         <f t="shared" si="93"/>
@@ -16613,7 +16584,7 @@
       </c>
       <c r="Z293">
         <f t="shared" si="94"/>
-        <v>53.810182176746501</v>
+        <v>31.464054287640607</v>
       </c>
     </row>
     <row r="294" spans="1:27" x14ac:dyDescent="0.2">
@@ -16630,42 +16601,44 @@
         <v>0</v>
       </c>
       <c r="L294">
-        <f>$AF$32</f>
-        <v>0.8</v>
+        <f>$AF$28</f>
+        <v>0.9</v>
       </c>
       <c r="N294">
-        <f>$AF$60</f>
-        <v>0.7</v>
+        <f>$AF$56</f>
+        <v>0.75</v>
       </c>
       <c r="O294">
         <f t="shared" si="89"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="Q294">
-        <f>$AF$87</f>
-        <v>75</v>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="P294" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q294" s="2">
+        <v>76</v>
       </c>
       <c r="R294">
         <f t="shared" si="95"/>
-        <v>1.6857229733976102</v>
+        <v>1.8175802556295724</v>
       </c>
       <c r="S294">
         <f t="shared" si="90"/>
-        <v>0.72196269954680592</v>
+        <v>0.80210130091638532</v>
       </c>
       <c r="T294">
         <v>1</v>
       </c>
       <c r="U294">
         <f t="shared" si="91"/>
-        <v>1.2170291085622071</v>
+        <v>1.4578834875604161</v>
       </c>
       <c r="V294">
         <v>25</v>
       </c>
       <c r="W294">
         <f t="shared" si="92"/>
-        <v>2.4460147240969496E-2</v>
+        <v>2.8988209566135827E-2</v>
       </c>
       <c r="Y294">
         <f t="shared" si="93"/>
@@ -16673,7 +16646,7 @@
       </c>
       <c r="Z294">
         <f t="shared" si="94"/>
-        <v>55.799710893461658</v>
+        <v>66.12935307274735</v>
       </c>
     </row>
     <row r="295" spans="1:27" x14ac:dyDescent="0.2">
@@ -16696,42 +16669,44 @@
         <v>0</v>
       </c>
       <c r="L295">
-        <f>$AG$29</f>
-        <v>2.5</v>
+        <f>$AG$25</f>
+        <v>4</v>
       </c>
       <c r="N295">
-        <f>$AG$57</f>
-        <v>0.75</v>
+        <f>$AG$53</f>
+        <v>0.7</v>
       </c>
       <c r="O295">
         <f t="shared" si="89"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q295">
-        <f>$AG$84</f>
-        <v>55</v>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="P295" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q295" s="2">
+        <v>75</v>
       </c>
       <c r="R295">
         <f t="shared" si="95"/>
-        <v>1.2959122541335131</v>
+        <v>1.6857229733976102</v>
       </c>
       <c r="S295">
         <f t="shared" si="90"/>
-        <v>0.99999627334682795</v>
+        <v>0.99999999999998734</v>
       </c>
       <c r="T295">
         <v>1</v>
       </c>
       <c r="U295">
         <f t="shared" si="91"/>
-        <v>1.2959074247180005</v>
+        <v>1.6857229733975889</v>
       </c>
       <c r="V295">
         <v>50</v>
       </c>
       <c r="W295">
         <f t="shared" si="92"/>
-        <v>2.5943059584698412E-2</v>
+        <v>3.3271591899874671E-2</v>
       </c>
       <c r="Y295">
         <f t="shared" si="93"/>
@@ -16739,7 +16714,7 @@
       </c>
       <c r="Z295">
         <f t="shared" si="94"/>
-        <v>118.36520935518651</v>
+        <v>151.80163804317817</v>
       </c>
     </row>
     <row r="296" spans="1:27" x14ac:dyDescent="0.2">
@@ -16756,24 +16731,26 @@
         <v>0</v>
       </c>
       <c r="L296">
-        <f>$AG$30</f>
+        <f>$AG$26</f>
         <v>2.5</v>
       </c>
       <c r="N296">
-        <f>$AG$58</f>
+        <f>$AG$54</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O296">
         <f t="shared" si="89"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="Q296">
-        <f>$AG$85</f>
-        <v>55</v>
+      <c r="P296" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q296" s="2">
+        <v>74</v>
       </c>
       <c r="R296">
         <f t="shared" si="95"/>
-        <v>0.95969823125361531</v>
+        <v>1.3460784869379241</v>
       </c>
       <c r="S296">
         <f t="shared" si="90"/>
@@ -16784,14 +16761,14 @@
       </c>
       <c r="U296">
         <f t="shared" si="91"/>
-        <v>0.95969465479115756</v>
+        <v>1.3460734705702608</v>
       </c>
       <c r="V296">
         <v>60</v>
       </c>
       <c r="W296">
         <f t="shared" si="92"/>
-        <v>1.9622259510073764E-2</v>
+        <v>2.6886181246720906E-2</v>
       </c>
       <c r="Y296">
         <f t="shared" si="93"/>
@@ -16799,7 +16776,7 @@
       </c>
       <c r="Z296">
         <f t="shared" si="94"/>
-        <v>107.43187081765385</v>
+        <v>147.20184232579695</v>
       </c>
     </row>
     <row r="297" spans="1:27" x14ac:dyDescent="0.2">
@@ -16816,42 +16793,44 @@
         <v>0</v>
       </c>
       <c r="L297">
-        <f>$AG$31</f>
-        <v>1.3</v>
+        <f>$AG$27</f>
+        <v>0.7</v>
       </c>
       <c r="N297">
-        <f>$AG$59</f>
-        <v>0.67</v>
+        <f>$AG$55</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O297">
         <f t="shared" si="89"/>
-        <v>0.53125000000000011</v>
-      </c>
-      <c r="Q297">
-        <f>$AG$86</f>
-        <v>50</v>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="P297" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q297" s="2">
+        <v>73</v>
       </c>
       <c r="R297">
         <f t="shared" si="95"/>
-        <v>1.052440031254225</v>
+        <v>1.3247455344549881</v>
       </c>
       <c r="S297">
         <f t="shared" si="90"/>
-        <v>0.96595254526540064</v>
+        <v>0.62468890114860043</v>
       </c>
       <c r="T297">
         <v>1</v>
       </c>
       <c r="U297">
         <f t="shared" si="91"/>
-        <v>1.0166071269292165</v>
+        <v>0.82755383222020196</v>
       </c>
       <c r="V297">
         <v>55</v>
       </c>
       <c r="W297">
         <f t="shared" si="92"/>
-        <v>2.0692213986269272E-2</v>
+        <v>1.7138012045739798E-2</v>
       </c>
       <c r="Y297">
         <f t="shared" si="93"/>
@@ -16859,7 +16838,7 @@
       </c>
       <c r="Z297">
         <f t="shared" si="94"/>
-        <v>103.8490489435889</v>
+        <v>86.011397954556614</v>
       </c>
     </row>
     <row r="298" spans="1:27" x14ac:dyDescent="0.2">
@@ -16876,42 +16855,44 @@
         <v>0</v>
       </c>
       <c r="L298">
-        <f>$AG$32</f>
-        <v>0.8</v>
+        <f>$AG$28</f>
+        <v>0.9</v>
       </c>
       <c r="N298">
-        <f>$AG$60</f>
-        <v>0.7</v>
+        <f>$AG$56</f>
+        <v>0.75</v>
       </c>
       <c r="O298">
         <f t="shared" si="89"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="Q298">
-        <f>$AG$87</f>
-        <v>45</v>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="P298" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q298" s="2">
+        <v>72</v>
       </c>
       <c r="R298">
         <f t="shared" si="95"/>
-        <v>0.98919258792655118</v>
+        <v>1.71499825233277</v>
       </c>
       <c r="S298">
         <f t="shared" si="90"/>
-        <v>0.72196269954680592</v>
+        <v>0.80210130091638532</v>
       </c>
       <c r="T298">
         <v>1</v>
       </c>
       <c r="U298">
         <f t="shared" si="91"/>
-        <v>0.71416015115114406</v>
+        <v>1.375602329265442</v>
       </c>
       <c r="V298">
         <v>55</v>
       </c>
       <c r="W298">
         <f t="shared" si="92"/>
-        <v>1.5006210841641509E-2</v>
+        <v>2.7441323790190313E-2</v>
       </c>
       <c r="Y298">
         <f t="shared" si="93"/>
@@ -16919,7 +16900,7 @@
       </c>
       <c r="Z298">
         <f t="shared" si="94"/>
-        <v>75.312420661488332</v>
+        <v>137.72114377201763</v>
       </c>
     </row>
     <row r="299" spans="1:27" x14ac:dyDescent="0.2">
@@ -16933,57 +16914,59 @@
         <v>80</v>
       </c>
       <c r="G299">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H299">
         <v>87</v>
       </c>
       <c r="I299">
         <f>(G299/100*MIN(H299,100)/100)</f>
-        <v>0.69600000000000006</v>
+        <v>0.80040000000000011</v>
       </c>
       <c r="J299">
         <f>$AF$3</f>
         <v>1.3</v>
       </c>
       <c r="L299">
-        <f>$AH$29</f>
-        <v>2.5</v>
+        <f>$AH$25</f>
+        <v>4</v>
       </c>
       <c r="N299">
-        <f>$AH$57</f>
-        <v>0.75</v>
+        <f>$AH$53</f>
+        <v>0.7</v>
       </c>
       <c r="O299">
         <f t="shared" si="89"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q299">
-        <f>$AH$84</f>
-        <v>45</v>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="P299" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q299" s="2">
+        <v>71</v>
       </c>
       <c r="R299">
         <f>(104.7 * O299 + 0.307 * Q299- 15) * POWER(Q299, 0.75) * 10^-3</f>
-        <v>1.0615017285371116</v>
+        <v>1.5877982261232466</v>
       </c>
       <c r="S299">
         <f t="shared" si="90"/>
-        <v>0.99999627334682795</v>
+        <v>0.99999999999998734</v>
       </c>
       <c r="T299">
         <f>(I299 * J299) + (1 - I299)</f>
-        <v>1.2088000000000001</v>
+        <v>1.2401200000000001</v>
       </c>
       <c r="U299">
         <f t="shared" si="91"/>
-        <v>1.2831385076256505</v>
+        <v>1.9690603361799357</v>
       </c>
       <c r="V299">
         <v>60</v>
       </c>
       <c r="W299">
         <f t="shared" si="92"/>
-        <v>2.5703003943362231E-2</v>
+        <v>3.8598334320182788E-2</v>
       </c>
       <c r="Y299">
         <f t="shared" si="93"/>
@@ -16991,7 +16974,7 @@
       </c>
       <c r="Z299">
         <f t="shared" si="94"/>
-        <v>140.72394658990822</v>
+        <v>211.32588040300078</v>
       </c>
     </row>
     <row r="300" spans="1:27" x14ac:dyDescent="0.2">
@@ -16999,38 +16982,36 @@
         <v>81</v>
       </c>
       <c r="G300">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H300">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I300">
         <f>(G300/100*MIN(H300,100)/100)</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="J300">
-        <f>$AF$3</f>
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L300">
-        <f>$AH$30</f>
+        <f>$AH$26</f>
         <v>2.5</v>
       </c>
       <c r="N300">
-        <f>$AH$58</f>
+        <f>$AH$54</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O300">
         <f t="shared" si="89"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="Q300">
-        <f>$AH$85</f>
-        <v>45</v>
+      <c r="P300" s="2">
+        <v>70</v>
+      </c>
+      <c r="Q300" s="2">
+        <v>70</v>
       </c>
       <c r="R300">
         <f t="shared" ref="R300:R314" si="96">(104.7 * O300 + 0.307 * Q300- 15) * POWER(Q300, 0.75) * 10^-3</f>
-        <v>0.77226516609487061</v>
+        <v>1.2614122912776211</v>
       </c>
       <c r="S300">
         <f t="shared" si="90"/>
@@ -17038,18 +17019,18 @@
       </c>
       <c r="T300">
         <f t="shared" ref="T300:T306" si="97">(I300 * J300) + (1 - I300)</f>
-        <v>1.0024</v>
+        <v>1</v>
       </c>
       <c r="U300">
         <f t="shared" si="91"/>
-        <v>0.77411571762195275</v>
+        <v>1.2614075904315045</v>
       </c>
       <c r="V300">
         <v>70</v>
       </c>
       <c r="W300">
         <f t="shared" si="92"/>
-        <v>1.6133375491292713E-2</v>
+        <v>2.5294462700112288E-2</v>
       </c>
       <c r="Y300">
         <f t="shared" si="93"/>
@@ -17057,7 +17038,7 @@
       </c>
       <c r="Z300">
         <f t="shared" si="94"/>
-        <v>103.05193595063221</v>
+        <v>161.56838049696725</v>
       </c>
     </row>
     <row r="301" spans="1:27" x14ac:dyDescent="0.2">
@@ -17071,32 +17052,34 @@
         <v>0</v>
       </c>
       <c r="I301">
-        <f t="shared" ref="I301:I304" si="98">(G301/100*MIN(H301,100)/100)</f>
+        <f t="shared" ref="I301:I303" si="98">(G301/100*MIN(H301,100)/100)</f>
         <v>0</v>
       </c>
       <c r="L301">
-        <f>$AH$31</f>
-        <v>1.3</v>
+        <f>$AH$27</f>
+        <v>0.7</v>
       </c>
       <c r="N301">
-        <f>$AH$59</f>
-        <v>0.67</v>
+        <f>$AH$55</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O301">
         <f t="shared" si="89"/>
-        <v>0.53125000000000011</v>
-      </c>
-      <c r="Q301">
-        <f>$AH$86</f>
-        <v>45</v>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="P301" s="2">
+        <v>69</v>
+      </c>
+      <c r="Q301" s="2">
+        <v>69</v>
       </c>
       <c r="R301">
         <f t="shared" si="96"/>
-        <v>0.94580710356021536</v>
+        <v>1.2405230861491703</v>
       </c>
       <c r="S301">
         <f t="shared" si="90"/>
-        <v>0.96595254526540064</v>
+        <v>0.62468890114860043</v>
       </c>
       <c r="T301">
         <f t="shared" si="97"/>
@@ -17104,14 +17087,14 @@
       </c>
       <c r="U301">
         <f t="shared" si="91"/>
-        <v>0.91360477901408643</v>
+        <v>0.77494100353599582</v>
       </c>
       <c r="V301">
         <v>60</v>
       </c>
       <c r="W301">
         <f t="shared" si="92"/>
-        <v>1.8755769845464829E-2</v>
+        <v>1.6148890866476723E-2</v>
       </c>
       <c r="Y301">
         <f t="shared" si="93"/>
@@ -17119,7 +17102,7 @@
       </c>
       <c r="Z301">
         <f t="shared" si="94"/>
-        <v>102.68783990391994</v>
+        <v>88.415177493960059</v>
       </c>
     </row>
     <row r="302" spans="1:27" x14ac:dyDescent="0.2">
@@ -17127,57 +17110,55 @@
         <v>83</v>
       </c>
       <c r="G302">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H302">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I302">
         <f t="shared" si="98"/>
-        <v>2E-3</v>
-      </c>
-      <c r="J302">
-        <f>$AF$3</f>
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L302">
-        <f>$AH$32</f>
-        <v>0.8</v>
+        <f>$AH$28</f>
+        <v>0.9</v>
       </c>
       <c r="N302">
-        <f>$AH$60</f>
-        <v>0.7</v>
+        <f>$AH$56</f>
+        <v>0.75</v>
       </c>
       <c r="O302">
         <f t="shared" si="89"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="Q302">
-        <f>$AH$87</f>
-        <v>50</v>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="P302" s="2">
+        <v>68</v>
+      </c>
+      <c r="Q302" s="2">
+        <v>68</v>
       </c>
       <c r="R302">
         <f t="shared" si="96"/>
-        <v>1.0993929471578776</v>
+        <v>1.6139528553516362</v>
       </c>
       <c r="S302">
         <f t="shared" si="90"/>
-        <v>0.72196269954680592</v>
+        <v>0.80210130091638532</v>
       </c>
       <c r="T302">
         <f t="shared" si="97"/>
-        <v>1.0005999999999999</v>
+        <v>1</v>
       </c>
       <c r="U302">
         <f t="shared" si="91"/>
-        <v>0.79419693241281586</v>
+        <v>1.2945536848952621</v>
       </c>
       <c r="V302">
         <v>50</v>
       </c>
       <c r="W302">
         <f t="shared" si="92"/>
-        <v>1.6510902329360939E-2</v>
+        <v>2.5917609276030932E-2</v>
       </c>
       <c r="Y302">
         <f t="shared" si="93"/>
@@ -17185,7 +17166,7 @@
       </c>
       <c r="Z302">
         <f t="shared" si="94"/>
-        <v>75.33099187770928</v>
+        <v>118.24909232189113</v>
       </c>
     </row>
     <row r="303" spans="1:27" x14ac:dyDescent="0.2">
@@ -17199,57 +17180,59 @@
         <v>80</v>
       </c>
       <c r="G303">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H303">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I303">
         <f t="shared" si="98"/>
-        <v>0.78299999999999992</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="J303">
         <f>$AF$3</f>
         <v>1.3</v>
       </c>
       <c r="L303">
-        <f>$AI$29</f>
-        <v>2.5</v>
+        <f>$AI$25</f>
+        <v>4</v>
       </c>
       <c r="N303">
-        <f>$AI$57</f>
-        <v>0.75</v>
+        <f>$AI$53</f>
+        <v>0.7</v>
       </c>
       <c r="O303">
         <f t="shared" si="89"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q303">
-        <f>$AI$84</f>
-        <v>50</v>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="P303" s="2">
+        <v>67</v>
+      </c>
+      <c r="Q303" s="2">
+        <v>67</v>
       </c>
       <c r="R303">
         <f t="shared" si="96"/>
-        <v>1.1776478069972991</v>
+        <v>1.4914665181818776</v>
       </c>
       <c r="S303">
         <f t="shared" si="90"/>
-        <v>0.99999627334682795</v>
+        <v>0.99999999999998734</v>
       </c>
       <c r="T303">
         <f t="shared" si="97"/>
-        <v>1.2349000000000001</v>
+        <v>1.2507999999999999</v>
       </c>
       <c r="U303">
         <f t="shared" si="91"/>
-        <v>1.4542718572739379</v>
+        <v>1.8655263209418687</v>
       </c>
       <c r="V303">
         <v>40</v>
       </c>
       <c r="W303">
         <f t="shared" si="92"/>
-        <v>2.8920310916750035E-2</v>
+        <v>3.6651894833707128E-2</v>
       </c>
       <c r="Y303">
         <f t="shared" si="93"/>
@@ -17257,7 +17240,7 @@
       </c>
       <c r="Z303">
         <f t="shared" si="94"/>
-        <v>105.55913484613764</v>
+        <v>133.779416143031</v>
       </c>
     </row>
     <row r="304" spans="1:27" x14ac:dyDescent="0.2">
@@ -17265,38 +17248,35 @@
         <v>81</v>
       </c>
       <c r="G304">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I304">
-        <f t="shared" si="98"/>
-        <v>1.5000000000000002E-3</v>
-      </c>
-      <c r="J304">
-        <f>$AF$3</f>
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L304">
-        <f>$AI$30</f>
+        <f>$AI$26</f>
         <v>2.5</v>
       </c>
       <c r="N304">
-        <f>$AI$58</f>
+        <f>$AI$54</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O304">
         <f t="shared" si="89"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="Q304">
-        <f>$AI$85</f>
-        <v>50</v>
+      <c r="P304" s="2">
+        <v>66</v>
+      </c>
+      <c r="Q304" s="2">
+        <v>66</v>
       </c>
       <c r="R304">
         <f t="shared" si="96"/>
-        <v>0.8646283676396137</v>
+        <v>1.1785209149153895</v>
       </c>
       <c r="S304">
         <f t="shared" si="90"/>
@@ -17304,18 +17284,18 @@
       </c>
       <c r="T304">
         <f t="shared" si="97"/>
-        <v>1.0004500000000001</v>
+        <v>1</v>
       </c>
       <c r="U304">
         <f t="shared" si="91"/>
-        <v>0.86501422678502615</v>
+        <v>1.1785165229766836</v>
       </c>
       <c r="V304">
         <v>45</v>
       </c>
       <c r="W304">
         <f t="shared" si="92"/>
-        <v>1.7842267463558492E-2</v>
+        <v>2.3736110631961654E-2</v>
       </c>
       <c r="Y304">
         <f t="shared" si="93"/>
@@ -17323,7 +17303,7 @@
       </c>
       <c r="Z304">
         <f t="shared" si="94"/>
-        <v>73.26481077223707</v>
+        <v>97.466404282492547</v>
       </c>
     </row>
     <row r="305" spans="1:26" x14ac:dyDescent="0.2">
@@ -17340,28 +17320,30 @@
         <v>0</v>
       </c>
       <c r="L305">
-        <f>$AI$31</f>
-        <v>1.3</v>
+        <f>$AI$27</f>
+        <v>0.7</v>
       </c>
       <c r="N305">
-        <f>$AI$59</f>
-        <v>0.67</v>
+        <f>$AI$55</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O305">
         <f t="shared" si="89"/>
-        <v>0.53125000000000011</v>
-      </c>
-      <c r="Q305">
-        <f>$AI$86</f>
-        <v>50</v>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="P305" s="2">
+        <v>65</v>
+      </c>
+      <c r="Q305" s="2">
+        <v>65</v>
       </c>
       <c r="R305">
         <f t="shared" si="96"/>
-        <v>1.052440031254225</v>
+        <v>1.1580752413958724</v>
       </c>
       <c r="S305">
         <f t="shared" si="90"/>
-        <v>0.96595254526540064</v>
+        <v>0.62468890114860043</v>
       </c>
       <c r="T305">
         <f t="shared" si="97"/>
@@ -17369,14 +17351,14 @@
       </c>
       <c r="U305">
         <f t="shared" si="91"/>
-        <v>1.0166071269292165</v>
+        <v>0.72343674999498764</v>
       </c>
       <c r="V305">
         <v>40</v>
       </c>
       <c r="W305">
         <f t="shared" si="92"/>
-        <v>2.0692213986269272E-2</v>
+        <v>1.5180610899905769E-2</v>
       </c>
       <c r="Y305">
         <f t="shared" si="93"/>
@@ -17384,7 +17366,7 @@
       </c>
       <c r="Z305">
         <f t="shared" si="94"/>
-        <v>75.52658104988285</v>
+        <v>55.409229784656056</v>
       </c>
     </row>
     <row r="306" spans="1:26" x14ac:dyDescent="0.2">
@@ -17401,28 +17383,30 @@
         <v>0</v>
       </c>
       <c r="L306">
-        <f>$AI$32</f>
-        <v>0.8</v>
+        <f>$AI$28</f>
+        <v>0.9</v>
       </c>
       <c r="N306">
-        <f>$AI$60</f>
-        <v>0.7</v>
+        <f>$AI$56</f>
+        <v>0.75</v>
       </c>
       <c r="O306">
         <f t="shared" si="89"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="Q306">
-        <f>$AI$87</f>
-        <v>55</v>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="P306" s="2">
+        <v>64</v>
+      </c>
+      <c r="Q306" s="2">
+        <v>64</v>
       </c>
       <c r="R306">
         <f t="shared" si="96"/>
-        <v>1.2118587484135388</v>
+        <v>1.5144257536366168</v>
       </c>
       <c r="S306">
         <f t="shared" si="90"/>
-        <v>0.72196269954680592</v>
+        <v>0.80210130091638532</v>
       </c>
       <c r="T306">
         <f t="shared" si="97"/>
@@ -17430,14 +17414,14 @@
       </c>
       <c r="U306">
         <f t="shared" si="91"/>
-        <v>0.87491681347405192</v>
+        <v>1.2147228671332075</v>
       </c>
       <c r="V306">
         <v>35</v>
       </c>
       <c r="W306">
         <f t="shared" si="92"/>
-        <v>1.8028436093312179E-2</v>
+        <v>2.4416789902104306E-2</v>
       </c>
       <c r="Y306">
         <f t="shared" si="93"/>
@@ -17445,7 +17429,7 @@
       </c>
       <c r="Z306">
         <f t="shared" si="94"/>
-        <v>57.578317773015769</v>
+        <v>77.981122749845625</v>
       </c>
     </row>
     <row r="307" spans="1:26" x14ac:dyDescent="0.2">
@@ -17468,42 +17452,44 @@
         <v>0</v>
       </c>
       <c r="L307">
-        <f>$AJ$29</f>
-        <v>2.5</v>
+        <f>$AJ$25</f>
+        <v>4</v>
       </c>
       <c r="N307">
-        <f>$AJ$57</f>
-        <v>0.75</v>
+        <f>$AJ$53</f>
+        <v>0.7</v>
       </c>
       <c r="O307">
         <f t="shared" si="89"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q307">
-        <f>$AJ$84</f>
-        <v>50</v>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="P307" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q307" s="2">
+        <v>63</v>
       </c>
       <c r="R307">
         <f t="shared" si="96"/>
-        <v>1.1776478069972991</v>
+        <v>1.3967130257259237</v>
       </c>
       <c r="S307">
         <f t="shared" si="90"/>
-        <v>0.99999627334682795</v>
+        <v>0.99999999999998734</v>
       </c>
       <c r="T307">
         <v>1</v>
       </c>
       <c r="U307">
         <f t="shared" si="91"/>
-        <v>1.1776434183123636</v>
+        <v>1.3967130257259059</v>
       </c>
       <c r="V307">
         <v>25</v>
       </c>
       <c r="W307">
         <f t="shared" si="92"/>
-        <v>2.3719696264272439E-2</v>
+        <v>2.7838204883647036E-2</v>
       </c>
       <c r="Y307">
         <f t="shared" si="93"/>
@@ -17511,7 +17497,7 @@
       </c>
       <c r="Z307">
         <f t="shared" si="94"/>
-        <v>54.110557102871503</v>
+        <v>63.505904890819806</v>
       </c>
     </row>
     <row r="308" spans="1:26" x14ac:dyDescent="0.2">
@@ -17528,24 +17514,26 @@
         <v>0</v>
       </c>
       <c r="L308">
-        <f>$AJ$30</f>
+        <f>$AJ$26</f>
         <v>2.5</v>
       </c>
       <c r="N308">
-        <f>$AJ$58</f>
+        <f>$AJ$54</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O308">
         <f t="shared" si="89"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="Q308">
-        <f>$AJ$85</f>
-        <v>50</v>
+      <c r="P308" s="2">
+        <v>62</v>
+      </c>
+      <c r="Q308" s="2">
+        <v>62</v>
       </c>
       <c r="R308">
         <f t="shared" si="96"/>
-        <v>0.8646283676396137</v>
+        <v>1.0974026986740544</v>
       </c>
       <c r="S308">
         <f t="shared" si="90"/>
@@ -17556,14 +17544,14 @@
       </c>
       <c r="U308">
         <f t="shared" si="91"/>
-        <v>0.86462514546956482</v>
+        <v>1.0973986090348062</v>
       </c>
       <c r="V308">
         <v>30</v>
       </c>
       <c r="W308">
         <f t="shared" si="92"/>
-        <v>1.7834952734827821E-2</v>
+        <v>2.2211093849854358E-2</v>
       </c>
       <c r="Y308">
         <f t="shared" si="93"/>
@@ -17571,7 +17559,7 @@
       </c>
       <c r="Z308">
         <f t="shared" si="94"/>
-        <v>48.823183111591163</v>
+        <v>60.802869413976303</v>
       </c>
     </row>
     <row r="309" spans="1:26" x14ac:dyDescent="0.2">
@@ -17588,42 +17576,44 @@
         <v>0</v>
       </c>
       <c r="L309">
-        <f>$AJ$31</f>
-        <v>1.3</v>
+        <f>$AJ$27</f>
+        <v>0.7</v>
       </c>
       <c r="N309">
-        <f>$AJ$59</f>
-        <v>0.67</v>
+        <f>$AJ$55</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O309">
         <f t="shared" si="89"/>
-        <v>0.53125000000000011</v>
-      </c>
-      <c r="Q309">
-        <f>$AJ$86</f>
-        <v>50</v>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="P309" s="2">
+        <v>61</v>
+      </c>
+      <c r="Q309" s="2">
+        <v>61</v>
       </c>
       <c r="R309">
         <f t="shared" si="96"/>
-        <v>1.052440031254225</v>
+        <v>1.0773997799878814</v>
       </c>
       <c r="S309">
         <f t="shared" si="90"/>
-        <v>0.96595254526540064</v>
+        <v>0.62468890114860043</v>
       </c>
       <c r="T309">
         <v>1</v>
       </c>
       <c r="U309">
         <f t="shared" si="91"/>
-        <v>1.0166071269292165</v>
+        <v>0.67303968465837349</v>
       </c>
       <c r="V309">
         <v>25</v>
       </c>
       <c r="W309">
         <f t="shared" si="92"/>
-        <v>2.0692213986269272E-2</v>
+        <v>1.4233146071577421E-2</v>
       </c>
       <c r="Y309">
         <f t="shared" si="93"/>
@@ -17631,7 +17621,7 @@
       </c>
       <c r="Z309">
         <f t="shared" si="94"/>
-        <v>47.204113156176774</v>
+        <v>32.469364475785987</v>
       </c>
     </row>
     <row r="310" spans="1:26" x14ac:dyDescent="0.2">
@@ -17648,42 +17638,44 @@
         <v>0</v>
       </c>
       <c r="L310">
-        <f>$AJ$32</f>
-        <v>0.8</v>
+        <f>$AJ$28</f>
+        <v>0.9</v>
       </c>
       <c r="N310">
-        <f>$AJ$60</f>
-        <v>0.7</v>
+        <f>$AJ$56</f>
+        <v>0.75</v>
       </c>
       <c r="O310">
         <f t="shared" si="89"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="Q310">
-        <f>$AJ$87</f>
-        <v>50</v>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="P310" s="2">
+        <v>60</v>
+      </c>
+      <c r="Q310" s="2">
+        <v>60</v>
       </c>
       <c r="R310">
         <f t="shared" si="96"/>
-        <v>1.0993929471578776</v>
+        <v>1.4163939481646182</v>
       </c>
       <c r="S310">
         <f t="shared" si="90"/>
-        <v>0.72196269954680592</v>
+        <v>0.80210130091638532</v>
       </c>
       <c r="T310">
         <v>1</v>
       </c>
       <c r="U310">
         <f t="shared" si="91"/>
-        <v>0.79372069999282024</v>
+        <v>1.1360914284329355</v>
       </c>
       <c r="V310">
         <v>20</v>
       </c>
       <c r="W310">
         <f t="shared" si="92"/>
-        <v>1.6501949159865022E-2</v>
+        <v>2.2938518854539191E-2</v>
       </c>
       <c r="Y310">
         <f t="shared" si="93"/>
@@ -17691,7 +17683,7 @@
       </c>
       <c r="Z310">
         <f t="shared" si="94"/>
-        <v>30.116057216753667</v>
+        <v>41.862796909534026</v>
       </c>
     </row>
     <row r="311" spans="1:26" x14ac:dyDescent="0.2">
@@ -17714,42 +17706,44 @@
         <v>0</v>
       </c>
       <c r="L311">
-        <f>$AK$29</f>
-        <v>2.5</v>
+        <f>$AK$25</f>
+        <v>4</v>
       </c>
       <c r="N311">
-        <f>$AK$57</f>
-        <v>0.75</v>
+        <f>$AK$53</f>
+        <v>0.7</v>
       </c>
       <c r="O311">
         <f t="shared" si="89"/>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="Q311">
-        <f>$AK$84</f>
-        <v>14</v>
+        <v>0.55510000000000004</v>
+      </c>
+      <c r="P311" s="2">
+        <v>59</v>
+      </c>
+      <c r="Q311" s="2">
+        <v>59</v>
       </c>
       <c r="R311">
         <f t="shared" si="96"/>
-        <v>0.3733079325984448</v>
+        <v>1.303518624930883</v>
       </c>
       <c r="S311">
         <f t="shared" si="90"/>
-        <v>0.99999627334682795</v>
+        <v>0.99999999999998734</v>
       </c>
       <c r="T311">
         <v>1</v>
       </c>
       <c r="U311">
         <f t="shared" si="91"/>
-        <v>0.37330654140925362</v>
+        <v>1.3035186249308666</v>
       </c>
       <c r="V311">
         <v>15</v>
       </c>
       <c r="W311">
         <f t="shared" si="92"/>
-        <v>8.5981629784939693E-3</v>
+        <v>2.6086150148700294E-2</v>
       </c>
       <c r="Y311">
         <f t="shared" si="93"/>
@@ -17757,7 +17751,7 @@
       </c>
       <c r="Z311">
         <f t="shared" si="94"/>
-        <v>11.76873557681362</v>
+        <v>35.705418016033526</v>
       </c>
     </row>
     <row r="312" spans="1:26" x14ac:dyDescent="0.2">
@@ -17774,24 +17768,26 @@
         <v>0</v>
       </c>
       <c r="L312">
-        <f>$AK$30</f>
+        <f>$AK$26</f>
         <v>2.5</v>
       </c>
       <c r="N312">
-        <f>$AK$58</f>
+        <f>$AK$54</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O312">
         <f t="shared" si="89"/>
         <v>0.43585000000000007</v>
       </c>
-      <c r="Q312">
-        <f>$AK$85</f>
-        <v>24</v>
+      <c r="P312" s="2">
+        <v>58</v>
+      </c>
+      <c r="Q312" s="2">
+        <v>58</v>
       </c>
       <c r="R312">
         <f t="shared" si="96"/>
-        <v>0.41205872426603418</v>
+        <v>1.0180535015422809</v>
       </c>
       <c r="S312">
         <f t="shared" si="90"/>
@@ -17802,14 +17798,14 @@
       </c>
       <c r="U312">
         <f t="shared" si="91"/>
-        <v>0.41205718866608232</v>
+        <v>1.0180497076099702</v>
       </c>
       <c r="V312">
         <v>45</v>
       </c>
       <c r="W312">
         <f t="shared" si="92"/>
-        <v>9.3266751469223488E-3</v>
+        <v>2.0719334503067441E-2</v>
       </c>
       <c r="Y312">
         <f t="shared" si="93"/>
@@ -17817,7 +17813,7 @@
       </c>
       <c r="Z312">
         <f t="shared" si="94"/>
-        <v>38.297659822049894</v>
+        <v>85.078767303220687</v>
       </c>
     </row>
     <row r="313" spans="1:26" x14ac:dyDescent="0.2">
@@ -17834,42 +17830,44 @@
         <v>0</v>
       </c>
       <c r="L313">
-        <f>$AK$31</f>
-        <v>1.3</v>
+        <f>$AK$27</f>
+        <v>0.7</v>
       </c>
       <c r="N313">
-        <f>$AK$59</f>
-        <v>0.67</v>
+        <f>$AK$55</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O313">
         <f t="shared" si="89"/>
-        <v>0.53125000000000011</v>
-      </c>
-      <c r="Q313">
-        <f>$AK$86</f>
-        <v>36</v>
+        <v>0.43585000000000007</v>
+      </c>
+      <c r="P313" s="2">
+        <v>57</v>
+      </c>
+      <c r="Q313" s="2">
+        <v>57</v>
       </c>
       <c r="R313">
         <f t="shared" si="96"/>
-        <v>0.75944776069416087</v>
+        <v>0.99849183106675043</v>
       </c>
       <c r="S313">
         <f t="shared" si="90"/>
-        <v>0.96595254526540064</v>
+        <v>0.62468890114860043</v>
       </c>
       <c r="T313">
         <v>1</v>
       </c>
       <c r="U313">
         <f t="shared" si="91"/>
-        <v>0.73359049743863358</v>
+        <v>0.62374676475494228</v>
       </c>
       <c r="V313">
         <v>40</v>
       </c>
       <c r="W313">
         <f t="shared" si="92"/>
-        <v>1.5371501351846312E-2</v>
+        <v>1.3306439177392914E-2</v>
       </c>
       <c r="Y313">
         <f t="shared" si="93"/>
@@ -17877,7 +17875,7 @@
       </c>
       <c r="Z313">
         <f t="shared" si="94"/>
-        <v>56.105979934239038</v>
+        <v>48.568502997484138</v>
       </c>
     </row>
     <row r="314" spans="1:26" x14ac:dyDescent="0.2">
@@ -17894,42 +17892,44 @@
         <v>0</v>
       </c>
       <c r="L314">
-        <f>$AK$32</f>
-        <v>0.8</v>
+        <f>$AK$28</f>
+        <v>0.9</v>
       </c>
       <c r="N314">
-        <f>$AK$60</f>
-        <v>0.7</v>
+        <f>$AK$56</f>
+        <v>0.75</v>
       </c>
       <c r="O314">
         <f t="shared" si="89"/>
-        <v>0.55510000000000004</v>
-      </c>
-      <c r="Q314">
-        <f>$AK$87</f>
-        <v>42</v>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="P314" s="2">
+        <v>56</v>
+      </c>
+      <c r="Q314" s="2">
+        <v>56</v>
       </c>
       <c r="R314">
         <f t="shared" si="96"/>
-        <v>0.92411404077093851</v>
+        <v>1.3198285488795851</v>
       </c>
       <c r="S314">
         <f t="shared" si="90"/>
-        <v>0.72196269954680592</v>
+        <v>0.80210130091638532</v>
       </c>
       <c r="T314">
         <v>1</v>
       </c>
       <c r="U314">
         <f t="shared" si="91"/>
-        <v>0.66717586756409386</v>
+        <v>1.0586361960429003</v>
       </c>
       <c r="V314">
         <v>30</v>
       </c>
       <c r="W314">
         <f t="shared" si="92"/>
-        <v>1.4122906310204965E-2</v>
+        <v>2.1482360485606526E-2</v>
       </c>
       <c r="Y314">
         <f t="shared" si="93"/>
@@ -17937,39 +17937,7 @@
       </c>
       <c r="Z314">
         <f t="shared" si="94"/>
-        <v>38.661456024186094</v>
-      </c>
-    </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="N325" t="s">
-        <v>80</v>
-      </c>
-      <c r="O325">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="N326" t="s">
-        <v>81</v>
-      </c>
-      <c r="O326">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="N327" t="s">
-        <v>82</v>
-      </c>
-      <c r="O327">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="N328" t="s">
-        <v>83</v>
-      </c>
-      <c r="O328">
-        <v>0.7</v>
+        <v>58.807961829347867</v>
       </c>
     </row>
     <row r="331" spans="1:27" x14ac:dyDescent="0.2">

--- a/packages/calculators/src/modules/test/3.4-sheep-enteric/3.4-sheep-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.4-sheep-enteric/3.4-sheep-enteric.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/3.4-sheep-enteric/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69718916-B6D8-D045-874B-15640B66E8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13520" yWindow="-20580" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
